--- a/research/traditional_assets/database/data/estonia/estonia_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_publishing_newspapers.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09745043250597285</v>
+        <v>0.0972915316409609</v>
       </c>
       <c r="C2">
-        <v>56.47750155661788</v>
+        <v>56.04636574304179</v>
       </c>
       <c r="D2">
-        <v>50.50750155661788</v>
+        <v>50.66336574304179</v>
       </c>
       <c r="E2">
-        <v>-29.7</v>
+        <v>-29.113</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5870000000000001</v>
       </c>
       <c r="G2">
         <v>5.97</v>
@@ -1445,28 +1445,28 @@
         <v>6.935</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0295261</v>
       </c>
       <c r="N2">
-        <v>6.935</v>
+        <v>6.9054739</v>
       </c>
       <c r="O2">
-        <v>1.387</v>
+        <v>1.38109478</v>
       </c>
       <c r="P2">
-        <v>5.548</v>
+        <v>5.52437912</v>
       </c>
       <c r="Q2">
-        <v>7.938</v>
+        <v>7.91437912</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09745043250597285</v>
+        <v>0.09786780973834434</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226993</v>
+        <v>0.9877071104903575</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>234.8769393858315</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0972915316409609</v>
+        <v>0.09713263077594894</v>
       </c>
       <c r="C3">
-        <v>56.04636574304179</v>
+        <v>55.61619488893388</v>
       </c>
       <c r="D3">
-        <v>50.66336574304179</v>
+        <v>50.82019488893388</v>
       </c>
       <c r="E3">
-        <v>-29.113</v>
+        <v>-28.526</v>
       </c>
       <c r="F3">
-        <v>0.5870000000000001</v>
+        <v>1.174</v>
       </c>
       <c r="G3">
         <v>5.97</v>
@@ -1527,28 +1527,28 @@
         <v>6.935</v>
       </c>
       <c r="M3">
-        <v>0.0295261</v>
+        <v>0.05905220000000001</v>
       </c>
       <c r="N3">
-        <v>6.9054739</v>
+        <v>6.8759478</v>
       </c>
       <c r="O3">
-        <v>1.38109478</v>
+        <v>1.37518956</v>
       </c>
       <c r="P3">
-        <v>5.52437912</v>
+        <v>5.50075824</v>
       </c>
       <c r="Q3">
-        <v>7.91437912</v>
+        <v>7.890758239999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09786780973834434</v>
+        <v>0.09829370487341729</v>
       </c>
       <c r="T3">
-        <v>0.9877071104903575</v>
+        <v>0.9957861838247025</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>234.8769393858315</v>
+        <v>117.4384696929157</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09713263077594894</v>
+        <v>0.096973729910937</v>
       </c>
       <c r="C4">
-        <v>55.61619488893388</v>
+        <v>55.18699798325554</v>
       </c>
       <c r="D4">
-        <v>50.82019488893388</v>
+        <v>50.97799798325555</v>
       </c>
       <c r="E4">
-        <v>-28.526</v>
+        <v>-27.939</v>
       </c>
       <c r="F4">
-        <v>1.174</v>
+        <v>1.761</v>
       </c>
       <c r="G4">
         <v>5.97</v>
@@ -1609,28 +1609,28 @@
         <v>6.935</v>
       </c>
       <c r="M4">
-        <v>0.05905220000000001</v>
+        <v>0.0885783</v>
       </c>
       <c r="N4">
-        <v>6.8759478</v>
+        <v>6.8464217</v>
       </c>
       <c r="O4">
-        <v>1.37518956</v>
+        <v>1.36928434</v>
       </c>
       <c r="P4">
-        <v>5.50075824</v>
+        <v>5.47713736</v>
       </c>
       <c r="Q4">
-        <v>7.890758239999999</v>
+        <v>7.867137359999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09829370487341729</v>
+        <v>0.09872838135148145</v>
       </c>
       <c r="T4">
-        <v>0.9957861838247025</v>
+        <v>1.004031835990683</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>117.4384696929157</v>
+        <v>78.2923131286105</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.096973729910937</v>
+        <v>0.09681482904592507</v>
       </c>
       <c r="C5">
-        <v>55.18699798325554</v>
+        <v>54.75878412696336</v>
       </c>
       <c r="D5">
-        <v>50.97799798325555</v>
+        <v>51.13678412696336</v>
       </c>
       <c r="E5">
-        <v>-27.939</v>
+        <v>-27.352</v>
       </c>
       <c r="F5">
-        <v>1.761</v>
+        <v>2.348</v>
       </c>
       <c r="G5">
         <v>5.97</v>
@@ -1691,28 +1691,28 @@
         <v>6.935</v>
       </c>
       <c r="M5">
-        <v>0.0885783</v>
+        <v>0.1181044</v>
       </c>
       <c r="N5">
-        <v>6.8464217</v>
+        <v>6.8168956</v>
       </c>
       <c r="O5">
-        <v>1.36928434</v>
+        <v>1.36337912</v>
       </c>
       <c r="P5">
-        <v>5.47713736</v>
+        <v>5.453516479999999</v>
       </c>
       <c r="Q5">
-        <v>7.867137359999999</v>
+        <v>7.843516479999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09872838135148145</v>
+        <v>0.09917211358950528</v>
       </c>
       <c r="T5">
-        <v>1.004031835990683</v>
+        <v>1.012449272576789</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>78.2923131286105</v>
+        <v>58.71923484645787</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09681482904592507</v>
+        <v>0.09665592818091311</v>
       </c>
       <c r="C6">
-        <v>54.75878412696336</v>
+        <v>54.33156253475878</v>
       </c>
       <c r="D6">
-        <v>51.13678412696336</v>
+        <v>51.29656253475878</v>
       </c>
       <c r="E6">
-        <v>-27.352</v>
+        <v>-26.765</v>
       </c>
       <c r="F6">
-        <v>2.348</v>
+        <v>2.935</v>
       </c>
       <c r="G6">
         <v>5.97</v>
@@ -1773,28 +1773,28 @@
         <v>6.935</v>
       </c>
       <c r="M6">
-        <v>0.1181044</v>
+        <v>0.1476305</v>
       </c>
       <c r="N6">
-        <v>6.8168956</v>
+        <v>6.7873695</v>
       </c>
       <c r="O6">
-        <v>1.36337912</v>
+        <v>1.3574739</v>
       </c>
       <c r="P6">
-        <v>5.453516479999999</v>
+        <v>5.4298956</v>
       </c>
       <c r="Q6">
-        <v>7.843516479999999</v>
+        <v>7.8198956</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09917211358950528</v>
+        <v>0.09962518755885591</v>
       </c>
       <c r="T6">
-        <v>1.012449272576789</v>
+        <v>1.021043918354181</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.71923484645787</v>
+        <v>46.97538787716629</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09665592818091311</v>
+        <v>0.09649702731590117</v>
       </c>
       <c r="C7">
-        <v>54.33156253475878</v>
+        <v>53.90534253687058</v>
       </c>
       <c r="D7">
-        <v>51.29656253475878</v>
+        <v>51.45734253687058</v>
       </c>
       <c r="E7">
-        <v>-26.765</v>
+        <v>-26.178</v>
       </c>
       <c r="F7">
-        <v>2.935</v>
+        <v>3.522</v>
       </c>
       <c r="G7">
         <v>5.97</v>
@@ -1855,28 +1855,28 @@
         <v>6.935</v>
       </c>
       <c r="M7">
-        <v>0.1476305</v>
+        <v>0.1771566</v>
       </c>
       <c r="N7">
-        <v>6.7873695</v>
+        <v>6.7578434</v>
       </c>
       <c r="O7">
-        <v>1.3574739</v>
+        <v>1.35156868</v>
       </c>
       <c r="P7">
-        <v>5.4298956</v>
+        <v>5.40627472</v>
       </c>
       <c r="Q7">
-        <v>7.8198956</v>
+        <v>7.79627472</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09962518755885591</v>
+        <v>0.1000879013998949</v>
       </c>
       <c r="T7">
-        <v>1.021043918354181</v>
+        <v>1.029821428935348</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.97538787716629</v>
+        <v>39.14615656430525</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09649702731590117</v>
+        <v>0.09633812645088922</v>
       </c>
       <c r="C8">
-        <v>53.90534253687058</v>
+        <v>53.48013358087119</v>
       </c>
       <c r="D8">
-        <v>51.45734253687058</v>
+        <v>51.61913358087119</v>
       </c>
       <c r="E8">
-        <v>-26.178</v>
+        <v>-25.591</v>
       </c>
       <c r="F8">
-        <v>3.522</v>
+        <v>4.109</v>
       </c>
       <c r="G8">
         <v>5.97</v>
@@ -1937,28 +1937,28 @@
         <v>6.935</v>
       </c>
       <c r="M8">
-        <v>0.1771566</v>
+        <v>0.2066827</v>
       </c>
       <c r="N8">
-        <v>6.7578434</v>
+        <v>6.7283173</v>
       </c>
       <c r="O8">
-        <v>1.35156868</v>
+        <v>1.34566346</v>
       </c>
       <c r="P8">
-        <v>5.40627472</v>
+        <v>5.38265384</v>
       </c>
       <c r="Q8">
-        <v>7.79627472</v>
+        <v>7.772653839999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1000879013998949</v>
+        <v>0.100560566076225</v>
       </c>
       <c r="T8">
-        <v>1.029821428935348</v>
+        <v>1.038787703184926</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.14615656430525</v>
+        <v>33.55384848369022</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09633812645088921</v>
+        <v>0.09617922558587728</v>
       </c>
       <c r="C9">
-        <v>53.4801335808712</v>
+        <v>53.05594523352722</v>
       </c>
       <c r="D9">
-        <v>51.61913358087121</v>
+        <v>51.78194523352722</v>
       </c>
       <c r="E9">
-        <v>-25.591</v>
+        <v>-25.004</v>
       </c>
       <c r="F9">
-        <v>4.109000000000001</v>
+        <v>4.696000000000001</v>
       </c>
       <c r="G9">
         <v>5.97</v>
@@ -2019,28 +2019,28 @@
         <v>6.935</v>
       </c>
       <c r="M9">
-        <v>0.2066827</v>
+        <v>0.2362088</v>
       </c>
       <c r="N9">
-        <v>6.7283173</v>
+        <v>6.6987912</v>
       </c>
       <c r="O9">
-        <v>1.34566346</v>
+        <v>1.33975824</v>
       </c>
       <c r="P9">
-        <v>5.38265384</v>
+        <v>5.35903296</v>
       </c>
       <c r="Q9">
-        <v>7.772653839999999</v>
+        <v>7.749032959999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.100560566076225</v>
+        <v>0.1010435060716057</v>
       </c>
       <c r="T9">
-        <v>1.038787703184926</v>
+        <v>1.047948896439931</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.55384848369021</v>
+        <v>29.35961742322894</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09617922558587728</v>
+        <v>0.09602032472086534</v>
       </c>
       <c r="C10">
-        <v>53.05594523352722</v>
+        <v>52.63278718268509</v>
       </c>
       <c r="D10">
-        <v>51.78194523352722</v>
+        <v>51.94578718268509</v>
       </c>
       <c r="E10">
-        <v>-25.004</v>
+        <v>-24.417</v>
       </c>
       <c r="F10">
-        <v>4.696000000000001</v>
+        <v>5.283</v>
       </c>
       <c r="G10">
         <v>5.97</v>
@@ -2101,28 +2101,28 @@
         <v>6.935</v>
       </c>
       <c r="M10">
-        <v>0.2362088</v>
+        <v>0.2657349</v>
       </c>
       <c r="N10">
-        <v>6.6987912</v>
+        <v>6.6692651</v>
       </c>
       <c r="O10">
-        <v>1.33975824</v>
+        <v>1.33385302</v>
       </c>
       <c r="P10">
-        <v>5.35903296</v>
+        <v>5.335412079999999</v>
       </c>
       <c r="Q10">
-        <v>7.749032959999999</v>
+        <v>7.725412079999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1010435060716057</v>
+        <v>0.101537060132819</v>
       </c>
       <c r="T10">
-        <v>1.047948896439931</v>
+        <v>1.057311434601638</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.35961742322894</v>
+        <v>26.09743770953683</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09602032472086534</v>
+        <v>0.09586142385585339</v>
       </c>
       <c r="C11">
-        <v>52.63278718268509</v>
+        <v>52.21066923919278</v>
       </c>
       <c r="D11">
-        <v>51.94578718268509</v>
+        <v>52.11066923919277</v>
       </c>
       <c r="E11">
-        <v>-24.417</v>
+        <v>-23.83</v>
       </c>
       <c r="F11">
-        <v>5.283</v>
+        <v>5.87</v>
       </c>
       <c r="G11">
         <v>5.97</v>
@@ -2183,28 +2183,28 @@
         <v>6.935</v>
       </c>
       <c r="M11">
-        <v>0.2657349</v>
+        <v>0.295261</v>
       </c>
       <c r="N11">
-        <v>6.6692651</v>
+        <v>6.639739</v>
       </c>
       <c r="O11">
-        <v>1.33385302</v>
+        <v>1.3279478</v>
       </c>
       <c r="P11">
-        <v>5.335412079999999</v>
+        <v>5.3117912</v>
       </c>
       <c r="Q11">
-        <v>7.725412079999999</v>
+        <v>7.7017912</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.101537060132819</v>
+        <v>0.1020415820620593</v>
       </c>
       <c r="T11">
-        <v>1.057311434601638</v>
+        <v>1.066882029166939</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.09743770953683</v>
+        <v>23.48769393858315</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09586142385585339</v>
+        <v>0.09570252299084143</v>
       </c>
       <c r="C12">
-        <v>52.21066923919277</v>
+        <v>51.78960133885794</v>
       </c>
       <c r="D12">
-        <v>52.11066923919277</v>
+        <v>52.27660133885794</v>
       </c>
       <c r="E12">
-        <v>-23.83</v>
+        <v>-23.243</v>
       </c>
       <c r="F12">
-        <v>5.870000000000001</v>
+        <v>6.457000000000001</v>
       </c>
       <c r="G12">
         <v>5.97</v>
@@ -2265,28 +2265,28 @@
         <v>6.935</v>
       </c>
       <c r="M12">
-        <v>0.2952610000000001</v>
+        <v>0.3247871</v>
       </c>
       <c r="N12">
-        <v>6.639739</v>
+        <v>6.6102129</v>
       </c>
       <c r="O12">
-        <v>1.3279478</v>
+        <v>1.32204258</v>
       </c>
       <c r="P12">
-        <v>5.3117912</v>
+        <v>5.28817032</v>
       </c>
       <c r="Q12">
-        <v>7.7017912</v>
+        <v>7.67817032</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1020415820620593</v>
+        <v>0.1025574415627432</v>
       </c>
       <c r="T12">
-        <v>1.066882029166939</v>
+        <v>1.076667693273033</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.48769393858315</v>
+        <v>21.35244903507559</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09570252299084143</v>
+        <v>0.09554362212582949</v>
       </c>
       <c r="C13">
-        <v>51.78960133885794</v>
+        <v>51.36959354444394</v>
       </c>
       <c r="D13">
-        <v>52.27660133885794</v>
+        <v>52.44359354444394</v>
       </c>
       <c r="E13">
-        <v>-23.243</v>
+        <v>-22.656</v>
       </c>
       <c r="F13">
-        <v>6.457000000000001</v>
+        <v>7.044</v>
       </c>
       <c r="G13">
         <v>5.97</v>
@@ -2347,28 +2347,28 @@
         <v>6.935</v>
       </c>
       <c r="M13">
-        <v>0.3247871</v>
+        <v>0.3543132</v>
       </c>
       <c r="N13">
-        <v>6.6102129</v>
+        <v>6.5806868</v>
       </c>
       <c r="O13">
-        <v>1.32204258</v>
+        <v>1.31613736</v>
       </c>
       <c r="P13">
-        <v>5.28817032</v>
+        <v>5.26454944</v>
       </c>
       <c r="Q13">
-        <v>7.67817032</v>
+        <v>7.654549439999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1025574415627432</v>
+        <v>0.1030850251429881</v>
       </c>
       <c r="T13">
-        <v>1.076667693273033</v>
+        <v>1.086675758836085</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.35244903507559</v>
+        <v>19.57307828215263</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09554362212582949</v>
+        <v>0.09538472126081757</v>
       </c>
       <c r="C14">
-        <v>51.36959354444394</v>
+        <v>50.95065604770402</v>
       </c>
       <c r="D14">
-        <v>52.44359354444394</v>
+        <v>52.61165604770402</v>
       </c>
       <c r="E14">
-        <v>-22.656</v>
+        <v>-22.069</v>
       </c>
       <c r="F14">
-        <v>7.044</v>
+        <v>7.631</v>
       </c>
       <c r="G14">
         <v>5.97</v>
@@ -2429,28 +2429,28 @@
         <v>6.935</v>
       </c>
       <c r="M14">
-        <v>0.3543132</v>
+        <v>0.3838393</v>
       </c>
       <c r="N14">
-        <v>6.5806868</v>
+        <v>6.5511607</v>
       </c>
       <c r="O14">
-        <v>1.31613736</v>
+        <v>1.31023214</v>
       </c>
       <c r="P14">
-        <v>5.26454944</v>
+        <v>5.24092856</v>
       </c>
       <c r="Q14">
-        <v>7.654549439999999</v>
+        <v>7.630928559999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1030850251429881</v>
+        <v>0.1036247370813995</v>
       </c>
       <c r="T14">
-        <v>1.086675758836085</v>
+        <v>1.09691389487185</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.57307828215263</v>
+        <v>18.06745687583319</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09538472126081757</v>
+        <v>0.09522582039580561</v>
       </c>
       <c r="C15">
-        <v>50.95065604770402</v>
+        <v>50.5327991714548</v>
       </c>
       <c r="D15">
-        <v>52.61165604770402</v>
+        <v>52.7807991714548</v>
       </c>
       <c r="E15">
-        <v>-22.069</v>
+        <v>-21.482</v>
       </c>
       <c r="F15">
-        <v>7.631</v>
+        <v>8.218000000000002</v>
       </c>
       <c r="G15">
         <v>5.97</v>
@@ -2511,28 +2511,28 @@
         <v>6.935</v>
       </c>
       <c r="M15">
-        <v>0.3838393</v>
+        <v>0.4133654</v>
       </c>
       <c r="N15">
-        <v>6.5511607</v>
+        <v>6.5216346</v>
       </c>
       <c r="O15">
-        <v>1.31023214</v>
+        <v>1.30432692</v>
       </c>
       <c r="P15">
-        <v>5.24092856</v>
+        <v>5.217307679999999</v>
       </c>
       <c r="Q15">
-        <v>7.630928559999999</v>
+        <v>7.607307679999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1036247370813995</v>
+        <v>0.1041770004602391</v>
       </c>
       <c r="T15">
-        <v>1.09691389487185</v>
+        <v>1.107390127094493</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.06745687583319</v>
+        <v>16.77692424184511</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09522582039580561</v>
+        <v>0.09506691953079366</v>
       </c>
       <c r="C16">
-        <v>50.5327991714548</v>
+        <v>50.1160333716898</v>
       </c>
       <c r="D16">
-        <v>52.7807991714548</v>
+        <v>52.9510333716898</v>
       </c>
       <c r="E16">
-        <v>-21.482</v>
+        <v>-20.895</v>
       </c>
       <c r="F16">
-        <v>8.218000000000002</v>
+        <v>8.805000000000001</v>
       </c>
       <c r="G16">
         <v>5.97</v>
@@ -2593,28 +2593,28 @@
         <v>6.935</v>
       </c>
       <c r="M16">
-        <v>0.4133654</v>
+        <v>0.4428915</v>
       </c>
       <c r="N16">
-        <v>6.5216346</v>
+        <v>6.4921085</v>
       </c>
       <c r="O16">
-        <v>1.30432692</v>
+        <v>1.2984217</v>
       </c>
       <c r="P16">
-        <v>5.217307679999999</v>
+        <v>5.1936868</v>
       </c>
       <c r="Q16">
-        <v>7.607307679999999</v>
+        <v>7.5836868</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1041770004602391</v>
+        <v>0.1047422582715219</v>
       </c>
       <c r="T16">
-        <v>1.107390127094493</v>
+        <v>1.118112858898845</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.77692424184511</v>
+        <v>15.6584626257221</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09506691953079366</v>
+        <v>0.0949080186657817</v>
       </c>
       <c r="C17">
-        <v>50.1160333716898</v>
+        <v>49.70036923973411</v>
       </c>
       <c r="D17">
-        <v>52.9510333716898</v>
+        <v>53.12236923973411</v>
       </c>
       <c r="E17">
-        <v>-20.895</v>
+        <v>-20.308</v>
       </c>
       <c r="F17">
-        <v>8.805</v>
+        <v>9.392000000000001</v>
       </c>
       <c r="G17">
         <v>5.97</v>
@@ -2675,28 +2675,28 @@
         <v>6.935</v>
       </c>
       <c r="M17">
-        <v>0.4428914999999999</v>
+        <v>0.4724176</v>
       </c>
       <c r="N17">
-        <v>6.4921085</v>
+        <v>6.4625824</v>
       </c>
       <c r="O17">
-        <v>1.2984217</v>
+        <v>1.29251648</v>
       </c>
       <c r="P17">
-        <v>5.1936868</v>
+        <v>5.17006592</v>
       </c>
       <c r="Q17">
-        <v>7.5836868</v>
+        <v>7.56006592</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1047422582715219</v>
+        <v>0.1053209746021211</v>
       </c>
       <c r="T17">
-        <v>1.118112858898845</v>
+        <v>1.129090893841396</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.6584626257221</v>
+        <v>14.67980871161447</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0949080186657817</v>
+        <v>0.09474911780076976</v>
       </c>
       <c r="C18">
-        <v>49.70036923973411</v>
+        <v>49.28581750444103</v>
       </c>
       <c r="D18">
-        <v>53.12236923973411</v>
+        <v>53.29481750444103</v>
       </c>
       <c r="E18">
-        <v>-20.308</v>
+        <v>-19.721</v>
       </c>
       <c r="F18">
-        <v>9.392000000000001</v>
+        <v>9.979000000000001</v>
       </c>
       <c r="G18">
         <v>5.97</v>
@@ -2757,28 +2757,28 @@
         <v>6.935</v>
       </c>
       <c r="M18">
-        <v>0.4724176</v>
+        <v>0.5019437</v>
       </c>
       <c r="N18">
-        <v>6.4625824</v>
+        <v>6.4330563</v>
       </c>
       <c r="O18">
-        <v>1.29251648</v>
+        <v>1.28661126</v>
       </c>
       <c r="P18">
-        <v>5.17006592</v>
+        <v>5.14644504</v>
       </c>
       <c r="Q18">
-        <v>7.56006592</v>
+        <v>7.536445039999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1053209746021211</v>
+        <v>0.1059136359045419</v>
       </c>
       <c r="T18">
-        <v>1.129090893841396</v>
+        <v>1.140333459746419</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.67980871161447</v>
+        <v>13.81629055210774</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09474911780076976</v>
+        <v>0.09459021693575784</v>
       </c>
       <c r="C19">
-        <v>49.28581750444103</v>
+        <v>48.87238903443154</v>
       </c>
       <c r="D19">
-        <v>53.29481750444103</v>
+        <v>53.46838903443155</v>
       </c>
       <c r="E19">
-        <v>-19.721</v>
+        <v>-19.134</v>
       </c>
       <c r="F19">
-        <v>9.979000000000001</v>
+        <v>10.566</v>
       </c>
       <c r="G19">
         <v>5.97</v>
@@ -2839,28 +2839,28 @@
         <v>6.935</v>
       </c>
       <c r="M19">
-        <v>0.5019437</v>
+        <v>0.5314698000000001</v>
       </c>
       <c r="N19">
-        <v>6.4330563</v>
+        <v>6.4035302</v>
       </c>
       <c r="O19">
-        <v>1.28661126</v>
+        <v>1.28070604</v>
       </c>
       <c r="P19">
-        <v>5.14644504</v>
+        <v>5.12282416</v>
       </c>
       <c r="Q19">
-        <v>7.536445039999999</v>
+        <v>7.512824159999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1059136359045419</v>
+        <v>0.1065207523606803</v>
       </c>
       <c r="T19">
-        <v>1.140333459746419</v>
+        <v>1.151850234575954</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.81629055210774</v>
+        <v>13.04871885476842</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09459021693575784</v>
+        <v>0.09465931607074587</v>
       </c>
       <c r="C20">
-        <v>48.87238903443154</v>
+        <v>48.20977153241549</v>
       </c>
       <c r="D20">
-        <v>53.46838903443155</v>
+        <v>53.39277153241549</v>
       </c>
       <c r="E20">
-        <v>-19.134</v>
+        <v>-18.547</v>
       </c>
       <c r="F20">
-        <v>10.566</v>
+        <v>11.153</v>
       </c>
       <c r="G20">
         <v>5.97</v>
@@ -2921,45 +2921,45 @@
         <v>6.935</v>
       </c>
       <c r="M20">
-        <v>0.5314698</v>
+        <v>0.5777254000000001</v>
       </c>
       <c r="N20">
-        <v>6.4035302</v>
+        <v>6.357274599999999</v>
       </c>
       <c r="O20">
-        <v>1.28070604</v>
+        <v>1.27145492</v>
       </c>
       <c r="P20">
-        <v>5.12282416</v>
+        <v>5.085819679999999</v>
       </c>
       <c r="Q20">
-        <v>7.512824159999999</v>
+        <v>7.475819679999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1065207523606803</v>
+        <v>0.1071428593465999</v>
       </c>
       <c r="T20">
-        <v>1.151850234575954</v>
+        <v>1.163651374216095</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.04871885476842</v>
+        <v>12.00397282169003</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09465931607074587</v>
+        <v>0.09451241520573395</v>
       </c>
       <c r="C21">
-        <v>48.20977153241549</v>
+        <v>47.78378683601662</v>
       </c>
       <c r="D21">
-        <v>53.39277153241549</v>
+        <v>53.55378683601662</v>
       </c>
       <c r="E21">
-        <v>-18.547</v>
+        <v>-17.96</v>
       </c>
       <c r="F21">
-        <v>11.153</v>
+        <v>11.74</v>
       </c>
       <c r="G21">
         <v>5.97</v>
@@ -3003,28 +3003,28 @@
         <v>6.935</v>
       </c>
       <c r="M21">
-        <v>0.5777254000000001</v>
+        <v>0.6081320000000001</v>
       </c>
       <c r="N21">
-        <v>6.357274599999999</v>
+        <v>6.326867999999999</v>
       </c>
       <c r="O21">
-        <v>1.27145492</v>
+        <v>1.2653736</v>
       </c>
       <c r="P21">
-        <v>5.085819679999999</v>
+        <v>5.061494399999999</v>
       </c>
       <c r="Q21">
-        <v>7.475819679999999</v>
+        <v>7.451494399999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1071428593465999</v>
+        <v>0.1077805190071674</v>
       </c>
       <c r="T21">
-        <v>1.163651374216095</v>
+        <v>1.175747542347239</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.00397282169003</v>
+        <v>11.40377418060552</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09451241520573395</v>
+        <v>0.09436551434072199</v>
       </c>
       <c r="C22">
-        <v>47.78378683601662</v>
+        <v>47.35877621711703</v>
       </c>
       <c r="D22">
-        <v>53.55378683601662</v>
+        <v>53.71577621711703</v>
       </c>
       <c r="E22">
-        <v>-17.96</v>
+        <v>-17.373</v>
       </c>
       <c r="F22">
-        <v>11.74</v>
+        <v>12.327</v>
       </c>
       <c r="G22">
         <v>5.97</v>
@@ -3085,28 +3085,28 @@
         <v>6.935</v>
       </c>
       <c r="M22">
-        <v>0.6081320000000001</v>
+        <v>0.6385386000000001</v>
       </c>
       <c r="N22">
-        <v>6.326867999999999</v>
+        <v>6.296461399999999</v>
       </c>
       <c r="O22">
-        <v>1.2653736</v>
+        <v>1.25929228</v>
       </c>
       <c r="P22">
-        <v>5.061494399999999</v>
+        <v>5.03716912</v>
       </c>
       <c r="Q22">
-        <v>7.451494399999999</v>
+        <v>7.427169119999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1077805190071674</v>
+        <v>0.108434321950281</v>
       </c>
       <c r="T22">
-        <v>1.175747542347239</v>
+        <v>1.18814994258297</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.40377418060552</v>
+        <v>10.8607373148624</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09436551434072199</v>
+        <v>0.09421861347571003</v>
       </c>
       <c r="C23">
-        <v>47.35877621711703</v>
+        <v>46.93474854169716</v>
       </c>
       <c r="D23">
-        <v>53.71577621711703</v>
+        <v>53.87874854169716</v>
       </c>
       <c r="E23">
-        <v>-17.373</v>
+        <v>-16.786</v>
       </c>
       <c r="F23">
-        <v>12.327</v>
+        <v>12.914</v>
       </c>
       <c r="G23">
         <v>5.97</v>
@@ -3167,28 +3167,28 @@
         <v>6.935</v>
       </c>
       <c r="M23">
-        <v>0.6385386</v>
+        <v>0.6689452</v>
       </c>
       <c r="N23">
-        <v>6.2964614</v>
+        <v>6.266054799999999</v>
       </c>
       <c r="O23">
-        <v>1.25929228</v>
+        <v>1.25321096</v>
       </c>
       <c r="P23">
-        <v>5.03716912</v>
+        <v>5.012843839999999</v>
       </c>
       <c r="Q23">
-        <v>7.427169119999999</v>
+        <v>7.402843839999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.108434321950281</v>
+        <v>0.1091048890714231</v>
       </c>
       <c r="T23">
-        <v>1.18814994258297</v>
+        <v>1.200870353081155</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.86073731486241</v>
+        <v>10.36706743691411</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09421861347571003</v>
+        <v>0.0940717126106981</v>
       </c>
       <c r="C24">
-        <v>46.93474854169716</v>
+        <v>46.51171278366154</v>
       </c>
       <c r="D24">
-        <v>53.87874854169716</v>
+        <v>54.04271278366154</v>
       </c>
       <c r="E24">
-        <v>-16.786</v>
+        <v>-16.199</v>
       </c>
       <c r="F24">
-        <v>12.914</v>
+        <v>13.501</v>
       </c>
       <c r="G24">
         <v>5.97</v>
@@ -3249,28 +3249,28 @@
         <v>6.935</v>
       </c>
       <c r="M24">
-        <v>0.6689452</v>
+        <v>0.6993518000000001</v>
       </c>
       <c r="N24">
-        <v>6.266054799999999</v>
+        <v>6.2356482</v>
       </c>
       <c r="O24">
-        <v>1.25321096</v>
+        <v>1.24712964</v>
       </c>
       <c r="P24">
-        <v>5.012843839999999</v>
+        <v>4.98851856</v>
       </c>
       <c r="Q24">
-        <v>7.402843839999999</v>
+        <v>7.37851856</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1091048890714231</v>
+        <v>0.1097928735203871</v>
       </c>
       <c r="T24">
-        <v>1.200870353081155</v>
+        <v>1.21392116385202</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.36706743691411</v>
+        <v>9.916325374439587</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0940717126106981</v>
+        <v>0.09425121174568617</v>
       </c>
       <c r="C25">
-        <v>46.51171278366154</v>
+        <v>45.72449859195066</v>
       </c>
       <c r="D25">
-        <v>54.04271278366154</v>
+        <v>53.84249859195066</v>
       </c>
       <c r="E25">
-        <v>-16.199</v>
+        <v>-15.612</v>
       </c>
       <c r="F25">
-        <v>13.501</v>
+        <v>14.088</v>
       </c>
       <c r="G25">
         <v>5.97</v>
@@ -3331,45 +3331,45 @@
         <v>6.935</v>
       </c>
       <c r="M25">
-        <v>0.6993518000000001</v>
+        <v>0.753708</v>
       </c>
       <c r="N25">
-        <v>6.2356482</v>
+        <v>6.181291999999999</v>
       </c>
       <c r="O25">
-        <v>1.24712964</v>
+        <v>1.2362584</v>
       </c>
       <c r="P25">
-        <v>4.98851856</v>
+        <v>4.945033599999999</v>
       </c>
       <c r="Q25">
-        <v>7.37851856</v>
+        <v>7.335033599999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1097928735203871</v>
+        <v>0.1104989628232713</v>
       </c>
       <c r="T25">
-        <v>1.21392116385202</v>
+        <v>1.227315417011592</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.916325374439587</v>
+        <v>9.20117605226427</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09425121174568614</v>
+        <v>0.0941179108806742</v>
       </c>
       <c r="C26">
-        <v>45.72449859195069</v>
+        <v>45.28604085104041</v>
       </c>
       <c r="D26">
-        <v>53.84249859195069</v>
+        <v>53.99104085104041</v>
       </c>
       <c r="E26">
-        <v>-15.612</v>
+        <v>-15.025</v>
       </c>
       <c r="F26">
-        <v>14.088</v>
+        <v>14.675</v>
       </c>
       <c r="G26">
         <v>5.97</v>
@@ -3413,28 +3413,28 @@
         <v>6.935</v>
       </c>
       <c r="M26">
-        <v>0.753708</v>
+        <v>0.7851125</v>
       </c>
       <c r="N26">
-        <v>6.181291999999999</v>
+        <v>6.149887499999999</v>
       </c>
       <c r="O26">
-        <v>1.2362584</v>
+        <v>1.2299775</v>
       </c>
       <c r="P26">
-        <v>4.945033599999999</v>
+        <v>4.91991</v>
       </c>
       <c r="Q26">
-        <v>7.335033599999999</v>
+        <v>7.309909999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1104989628232712</v>
+        <v>0.1112238811742323</v>
       </c>
       <c r="T26">
-        <v>1.227315417011592</v>
+        <v>1.241066850255419</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.20117605226427</v>
+        <v>8.8331290101737</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0941179108806742</v>
+        <v>0.09398461001566226</v>
       </c>
       <c r="C27">
-        <v>45.28604085104041</v>
+        <v>44.84840498299041</v>
       </c>
       <c r="D27">
-        <v>53.99104085104041</v>
+        <v>54.14040498299041</v>
       </c>
       <c r="E27">
-        <v>-15.025</v>
+        <v>-14.438</v>
       </c>
       <c r="F27">
-        <v>14.675</v>
+        <v>15.262</v>
       </c>
       <c r="G27">
         <v>5.97</v>
@@ -3495,28 +3495,28 @@
         <v>6.935</v>
       </c>
       <c r="M27">
-        <v>0.7851125</v>
+        <v>0.816517</v>
       </c>
       <c r="N27">
-        <v>6.149887499999999</v>
+        <v>6.118482999999999</v>
       </c>
       <c r="O27">
-        <v>1.2299775</v>
+        <v>1.2236966</v>
       </c>
       <c r="P27">
-        <v>4.91991</v>
+        <v>4.894786399999999</v>
       </c>
       <c r="Q27">
-        <v>7.309909999999999</v>
+        <v>7.284786399999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1112238811742323</v>
+        <v>0.1119683919130571</v>
       </c>
       <c r="T27">
-        <v>1.241066850255419</v>
+        <v>1.255189943857188</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.8331290101737</v>
+        <v>8.493393279013173</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09398461001566226</v>
+        <v>0.09385130915065031</v>
       </c>
       <c r="C28">
-        <v>44.84840498299041</v>
+        <v>44.41159782776189</v>
       </c>
       <c r="D28">
-        <v>54.14040498299041</v>
+        <v>54.29059782776189</v>
       </c>
       <c r="E28">
-        <v>-14.438</v>
+        <v>-13.851</v>
       </c>
       <c r="F28">
-        <v>15.262</v>
+        <v>15.849</v>
       </c>
       <c r="G28">
         <v>5.97</v>
@@ -3577,28 +3577,28 @@
         <v>6.935</v>
       </c>
       <c r="M28">
-        <v>0.816517</v>
+        <v>0.8479215000000001</v>
       </c>
       <c r="N28">
-        <v>6.118482999999999</v>
+        <v>6.0870785</v>
       </c>
       <c r="O28">
-        <v>1.2236966</v>
+        <v>1.2174157</v>
       </c>
       <c r="P28">
-        <v>4.894786399999999</v>
+        <v>4.8696628</v>
       </c>
       <c r="Q28">
-        <v>7.284786399999999</v>
+        <v>7.259662799999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1119683919130571</v>
+        <v>0.1127333002063703</v>
       </c>
       <c r="T28">
-        <v>1.255189943857188</v>
+        <v>1.269699971530238</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.493393279013173</v>
+        <v>8.178823157568241</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09385130915065031</v>
+        <v>0.09371800828563837</v>
       </c>
       <c r="C29">
-        <v>44.41159782776189</v>
+        <v>43.97562630142708</v>
       </c>
       <c r="D29">
-        <v>54.29059782776189</v>
+        <v>54.44162630142709</v>
       </c>
       <c r="E29">
-        <v>-13.851</v>
+        <v>-13.264</v>
       </c>
       <c r="F29">
-        <v>15.849</v>
+        <v>16.436</v>
       </c>
       <c r="G29">
         <v>5.97</v>
@@ -3659,28 +3659,28 @@
         <v>6.935</v>
       </c>
       <c r="M29">
-        <v>0.8479215000000001</v>
+        <v>0.8793260000000002</v>
       </c>
       <c r="N29">
-        <v>6.0870785</v>
+        <v>6.055674</v>
       </c>
       <c r="O29">
-        <v>1.2174157</v>
+        <v>1.2111348</v>
       </c>
       <c r="P29">
-        <v>4.8696628</v>
+        <v>4.8445392</v>
       </c>
       <c r="Q29">
-        <v>7.259662799999999</v>
+        <v>7.2345392</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1127333002063703</v>
+        <v>0.1135194559522755</v>
       </c>
       <c r="T29">
-        <v>1.269699971530238</v>
+        <v>1.284613055527539</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.178823157568241</v>
+        <v>7.886722330512232</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09371800828563837</v>
+        <v>0.09358470742062641</v>
       </c>
       <c r="C30">
-        <v>43.97562630142708</v>
+        <v>43.54049739723094</v>
       </c>
       <c r="D30">
-        <v>54.44162630142709</v>
+        <v>54.59349739723095</v>
       </c>
       <c r="E30">
-        <v>-13.264</v>
+        <v>-12.677</v>
       </c>
       <c r="F30">
-        <v>16.436</v>
+        <v>17.023</v>
       </c>
       <c r="G30">
         <v>5.97</v>
@@ -3741,28 +3741,28 @@
         <v>6.935</v>
       </c>
       <c r="M30">
-        <v>0.8793260000000002</v>
+        <v>0.9107305000000001</v>
       </c>
       <c r="N30">
-        <v>6.055674</v>
+        <v>6.024269499999999</v>
       </c>
       <c r="O30">
-        <v>1.2111348</v>
+        <v>1.2048539</v>
       </c>
       <c r="P30">
-        <v>4.8445392</v>
+        <v>4.819415599999999</v>
       </c>
       <c r="Q30">
-        <v>7.2345392</v>
+        <v>7.209415599999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1135194559522755</v>
+        <v>0.1143277569304597</v>
       </c>
       <c r="T30">
-        <v>1.284613055527539</v>
+        <v>1.299946226398004</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.886722330512232</v>
+        <v>7.614766388080775</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09358470742062641</v>
+        <v>0.09364340655561448</v>
       </c>
       <c r="C31">
-        <v>43.54049739723095</v>
+        <v>42.88651656739673</v>
       </c>
       <c r="D31">
-        <v>54.59349739723095</v>
+        <v>54.52651656739673</v>
       </c>
       <c r="E31">
-        <v>-12.677</v>
+        <v>-12.09</v>
       </c>
       <c r="F31">
-        <v>17.023</v>
+        <v>17.61</v>
       </c>
       <c r="G31">
         <v>5.97</v>
@@ -3823,45 +3823,45 @@
         <v>6.935</v>
       </c>
       <c r="M31">
-        <v>0.9107305</v>
+        <v>0.9562229999999999</v>
       </c>
       <c r="N31">
-        <v>6.0242695</v>
+        <v>5.978777</v>
       </c>
       <c r="O31">
-        <v>1.2048539</v>
+        <v>1.1957554</v>
       </c>
       <c r="P31">
-        <v>4.8194156</v>
+        <v>4.7830216</v>
       </c>
       <c r="Q31">
-        <v>7.2094156</v>
+        <v>7.173021599999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1143277569304597</v>
+        <v>0.1151591522223064</v>
       </c>
       <c r="T31">
-        <v>1.299946226398004</v>
+        <v>1.315717487864768</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.614766388080777</v>
+        <v>7.25249235795416</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09364340655561448</v>
+        <v>0.09351650569060252</v>
       </c>
       <c r="C32">
-        <v>42.88651656739673</v>
+        <v>42.44452848766093</v>
       </c>
       <c r="D32">
-        <v>54.52651656739673</v>
+        <v>54.67152848766094</v>
       </c>
       <c r="E32">
-        <v>-12.09</v>
+        <v>-11.503</v>
       </c>
       <c r="F32">
-        <v>17.61</v>
+        <v>18.197</v>
       </c>
       <c r="G32">
         <v>5.97</v>
@@ -3905,28 +3905,28 @@
         <v>6.935</v>
       </c>
       <c r="M32">
-        <v>0.9562229999999999</v>
+        <v>0.9880971</v>
       </c>
       <c r="N32">
-        <v>5.978777</v>
+        <v>5.9469029</v>
       </c>
       <c r="O32">
-        <v>1.1957554</v>
+        <v>1.18938058</v>
       </c>
       <c r="P32">
-        <v>4.7830216</v>
+        <v>4.75752232</v>
       </c>
       <c r="Q32">
-        <v>7.173021599999999</v>
+        <v>7.147522319999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1151591522223064</v>
+        <v>0.1160146459284095</v>
       </c>
       <c r="T32">
-        <v>1.315717487864768</v>
+        <v>1.331945887345061</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.25249235795416</v>
+        <v>7.018540991568541</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09351650569060252</v>
+        <v>0.09338960482559058</v>
       </c>
       <c r="C33">
-        <v>42.44452848766093</v>
+        <v>42.00331377589845</v>
       </c>
       <c r="D33">
-        <v>54.67152848766094</v>
+        <v>54.81731377589846</v>
       </c>
       <c r="E33">
-        <v>-11.503</v>
+        <v>-10.916</v>
       </c>
       <c r="F33">
-        <v>18.197</v>
+        <v>18.784</v>
       </c>
       <c r="G33">
         <v>5.97</v>
@@ -3987,28 +3987,28 @@
         <v>6.935</v>
       </c>
       <c r="M33">
-        <v>0.9880971</v>
+        <v>1.0199712</v>
       </c>
       <c r="N33">
-        <v>5.9469029</v>
+        <v>5.9150288</v>
       </c>
       <c r="O33">
-        <v>1.18938058</v>
+        <v>1.18300576</v>
       </c>
       <c r="P33">
-        <v>4.75752232</v>
+        <v>4.73202304</v>
       </c>
       <c r="Q33">
-        <v>7.147522319999999</v>
+        <v>7.122023039999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1160146459284095</v>
+        <v>0.1168953012141038</v>
       </c>
       <c r="T33">
-        <v>1.331945887345061</v>
+        <v>1.348651592692421</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.018540991568541</v>
+        <v>6.799211585582023</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09338960482559058</v>
+        <v>0.09326270396057863</v>
       </c>
       <c r="C34">
-        <v>42.00331377589845</v>
+        <v>41.56287863536308</v>
       </c>
       <c r="D34">
-        <v>54.81731377589846</v>
+        <v>54.96387863536308</v>
       </c>
       <c r="E34">
-        <v>-10.916</v>
+        <v>-10.329</v>
       </c>
       <c r="F34">
-        <v>18.784</v>
+        <v>19.371</v>
       </c>
       <c r="G34">
         <v>5.97</v>
@@ -4069,28 +4069,28 @@
         <v>6.935</v>
       </c>
       <c r="M34">
-        <v>1.0199712</v>
+        <v>1.0518453</v>
       </c>
       <c r="N34">
-        <v>5.9150288</v>
+        <v>5.8831547</v>
       </c>
       <c r="O34">
-        <v>1.18300576</v>
+        <v>1.17663094</v>
       </c>
       <c r="P34">
-        <v>4.73202304</v>
+        <v>4.70652376</v>
       </c>
       <c r="Q34">
-        <v>7.122023039999999</v>
+        <v>7.096523759999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1168953012141038</v>
+        <v>0.1178022447172815</v>
       </c>
       <c r="T34">
-        <v>1.348651592692421</v>
+        <v>1.365855975811345</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.799211585582023</v>
+        <v>6.593174870867417</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09326270396057863</v>
+        <v>0.0931358030955667</v>
       </c>
       <c r="C35">
-        <v>41.56287863536308</v>
+        <v>41.12322933582878</v>
       </c>
       <c r="D35">
-        <v>54.96387863536308</v>
+        <v>55.11122933582879</v>
       </c>
       <c r="E35">
-        <v>-10.329</v>
+        <v>-9.741999999999997</v>
       </c>
       <c r="F35">
-        <v>19.371</v>
+        <v>19.958</v>
       </c>
       <c r="G35">
         <v>5.97</v>
@@ -4151,28 +4151,28 @@
         <v>6.935</v>
       </c>
       <c r="M35">
-        <v>1.0518453</v>
+        <v>1.0837194</v>
       </c>
       <c r="N35">
-        <v>5.8831547</v>
+        <v>5.851280599999999</v>
       </c>
       <c r="O35">
-        <v>1.17663094</v>
+        <v>1.17025612</v>
       </c>
       <c r="P35">
-        <v>4.70652376</v>
+        <v>4.68102448</v>
       </c>
       <c r="Q35">
-        <v>7.096523759999999</v>
+        <v>7.071024479999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1178022447172815</v>
+        <v>0.1187366713569192</v>
       </c>
       <c r="T35">
-        <v>1.365855975811345</v>
+        <v>1.383581703873266</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.593174870867417</v>
+        <v>6.399257962900728</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0931358030955667</v>
+        <v>0.09300890223055475</v>
       </c>
       <c r="C36">
-        <v>41.12322933582878</v>
+        <v>40.68437221448404</v>
       </c>
       <c r="D36">
-        <v>55.11122933582879</v>
+        <v>55.25937221448405</v>
       </c>
       <c r="E36">
-        <v>-9.741999999999997</v>
+        <v>-9.154999999999998</v>
       </c>
       <c r="F36">
-        <v>19.958</v>
+        <v>20.545</v>
       </c>
       <c r="G36">
         <v>5.97</v>
@@ -4233,28 +4233,28 @@
         <v>6.935</v>
       </c>
       <c r="M36">
-        <v>1.0837194</v>
+        <v>1.1155935</v>
       </c>
       <c r="N36">
-        <v>5.851280599999999</v>
+        <v>5.819406499999999</v>
       </c>
       <c r="O36">
-        <v>1.17025612</v>
+        <v>1.1638813</v>
       </c>
       <c r="P36">
-        <v>4.68102448</v>
+        <v>4.6555252</v>
       </c>
       <c r="Q36">
-        <v>7.071024479999999</v>
+        <v>7.045525199999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1187366713569192</v>
+        <v>0.1196998495854688</v>
       </c>
       <c r="T36">
-        <v>1.383581703873266</v>
+        <v>1.401852838952478</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.399257962900728</v>
+        <v>6.216422021103564</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09300890223055475</v>
+        <v>0.09317000136554281</v>
       </c>
       <c r="C37">
-        <v>40.68437221448404</v>
+        <v>39.90944236843991</v>
       </c>
       <c r="D37">
-        <v>55.25937221448405</v>
+        <v>55.07144236843992</v>
       </c>
       <c r="E37">
-        <v>-9.154999999999998</v>
+        <v>-8.567999999999994</v>
       </c>
       <c r="F37">
-        <v>20.545</v>
+        <v>21.13200000000001</v>
       </c>
       <c r="G37">
         <v>5.97</v>
@@ -4315,45 +4315,45 @@
         <v>6.935</v>
       </c>
       <c r="M37">
-        <v>1.1155935</v>
+        <v>1.1685996</v>
       </c>
       <c r="N37">
-        <v>5.819406499999999</v>
+        <v>5.766400399999999</v>
       </c>
       <c r="O37">
-        <v>1.1638813</v>
+        <v>1.15328008</v>
       </c>
       <c r="P37">
-        <v>4.6555252</v>
+        <v>4.613120319999999</v>
       </c>
       <c r="Q37">
-        <v>7.045525199999999</v>
+        <v>7.003120319999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1196998495854688</v>
+        <v>0.1206931271336606</v>
       </c>
       <c r="T37">
-        <v>1.401852838952478</v>
+        <v>1.420694947002914</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.216422021103564</v>
+        <v>5.934453511707515</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09317000136554279</v>
+        <v>0.09305110050053086</v>
       </c>
       <c r="C38">
-        <v>39.90944236843993</v>
+        <v>39.46102204310779</v>
       </c>
       <c r="D38">
-        <v>55.07144236843993</v>
+        <v>55.21002204310779</v>
       </c>
       <c r="E38">
-        <v>-8.567999999999998</v>
+        <v>-7.980999999999998</v>
       </c>
       <c r="F38">
-        <v>21.132</v>
+        <v>21.719</v>
       </c>
       <c r="G38">
         <v>5.97</v>
@@ -4397,28 +4397,28 @@
         <v>6.935</v>
       </c>
       <c r="M38">
-        <v>1.1685996</v>
+        <v>1.2010607</v>
       </c>
       <c r="N38">
-        <v>5.766400399999999</v>
+        <v>5.733939299999999</v>
       </c>
       <c r="O38">
-        <v>1.15328008</v>
+        <v>1.14678786</v>
       </c>
       <c r="P38">
-        <v>4.613120319999999</v>
+        <v>4.58715144</v>
       </c>
       <c r="Q38">
-        <v>7.003120319999999</v>
+        <v>6.977151439999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1206931271336606</v>
+        <v>0.1217179373024299</v>
       </c>
       <c r="T38">
-        <v>1.420694947002914</v>
+        <v>1.440135217213682</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.934453511707517</v>
+        <v>5.774062876255962</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09305110050053086</v>
+        <v>0.09293219963551891</v>
       </c>
       <c r="C39">
-        <v>39.46102204310779</v>
+        <v>39.01330091040062</v>
       </c>
       <c r="D39">
-        <v>55.21002204310779</v>
+        <v>55.34930091040061</v>
       </c>
       <c r="E39">
-        <v>-7.980999999999998</v>
+        <v>-7.393999999999998</v>
       </c>
       <c r="F39">
-        <v>21.719</v>
+        <v>22.306</v>
       </c>
       <c r="G39">
         <v>5.97</v>
@@ -4479,28 +4479,28 @@
         <v>6.935</v>
       </c>
       <c r="M39">
-        <v>1.2010607</v>
+        <v>1.2335218</v>
       </c>
       <c r="N39">
-        <v>5.733939299999999</v>
+        <v>5.701478199999999</v>
       </c>
       <c r="O39">
-        <v>1.14678786</v>
+        <v>1.14029564</v>
       </c>
       <c r="P39">
-        <v>4.58715144</v>
+        <v>4.56118256</v>
       </c>
       <c r="Q39">
-        <v>6.977151439999999</v>
+        <v>6.951182559999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1217179373024299</v>
+        <v>0.1227758058637402</v>
       </c>
       <c r="T39">
-        <v>1.440135217213682</v>
+        <v>1.460202592915119</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.774062876255962</v>
+        <v>5.622113853196595</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09293219963551891</v>
+        <v>0.09281329877050698</v>
       </c>
       <c r="C40">
-        <v>39.01330091040062</v>
+        <v>38.56628427528163</v>
       </c>
       <c r="D40">
-        <v>55.34930091040061</v>
+        <v>55.48928427528163</v>
       </c>
       <c r="E40">
-        <v>-7.393999999999998</v>
+        <v>-6.806999999999999</v>
       </c>
       <c r="F40">
-        <v>22.306</v>
+        <v>22.893</v>
       </c>
       <c r="G40">
         <v>5.97</v>
@@ -4561,28 +4561,28 @@
         <v>6.935</v>
       </c>
       <c r="M40">
-        <v>1.2335218</v>
+        <v>1.2659829</v>
       </c>
       <c r="N40">
-        <v>5.701478199999999</v>
+        <v>5.6690171</v>
       </c>
       <c r="O40">
-        <v>1.14029564</v>
+        <v>1.13380342</v>
       </c>
       <c r="P40">
-        <v>4.56118256</v>
+        <v>4.53521368</v>
       </c>
       <c r="Q40">
-        <v>6.951182559999999</v>
+        <v>6.92521368</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1227758058637402</v>
+        <v>0.1238683586401754</v>
       </c>
       <c r="T40">
-        <v>1.460202592915119</v>
+        <v>1.480927915360867</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.622113853196595</v>
+        <v>5.477957087730015</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09281329877050698</v>
+        <v>0.09269439790549502</v>
       </c>
       <c r="C41">
-        <v>38.56628427528163</v>
+        <v>38.11997749651718</v>
       </c>
       <c r="D41">
-        <v>55.48928427528163</v>
+        <v>55.62997749651718</v>
       </c>
       <c r="E41">
-        <v>-6.806999999999999</v>
+        <v>-6.219999999999995</v>
       </c>
       <c r="F41">
-        <v>22.893</v>
+        <v>23.48</v>
       </c>
       <c r="G41">
         <v>5.97</v>
@@ -4643,28 +4643,28 @@
         <v>6.935</v>
       </c>
       <c r="M41">
-        <v>1.2659829</v>
+        <v>1.298444</v>
       </c>
       <c r="N41">
-        <v>5.6690171</v>
+        <v>5.636555999999999</v>
       </c>
       <c r="O41">
-        <v>1.13380342</v>
+        <v>1.1273112</v>
       </c>
       <c r="P41">
-        <v>4.53521368</v>
+        <v>4.509244799999999</v>
       </c>
       <c r="Q41">
-        <v>6.92521368</v>
+        <v>6.899244799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1238683586401754</v>
+        <v>0.1249973298424917</v>
       </c>
       <c r="T41">
-        <v>1.480927915360867</v>
+        <v>1.502344081888139</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.477957087730015</v>
+        <v>5.341008160536763</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09269439790549502</v>
+        <v>0.09257549704048307</v>
       </c>
       <c r="C42">
-        <v>38.11997749651718</v>
+        <v>37.6743859873603</v>
       </c>
       <c r="D42">
-        <v>55.62997749651718</v>
+        <v>55.7713859873603</v>
       </c>
       <c r="E42">
-        <v>-6.219999999999995</v>
+        <v>-5.632999999999996</v>
       </c>
       <c r="F42">
-        <v>23.48</v>
+        <v>24.067</v>
       </c>
       <c r="G42">
         <v>5.97</v>
@@ -4725,28 +4725,28 @@
         <v>6.935</v>
       </c>
       <c r="M42">
-        <v>1.298444</v>
+        <v>1.3309051</v>
       </c>
       <c r="N42">
-        <v>5.636555999999999</v>
+        <v>5.6040949</v>
       </c>
       <c r="O42">
-        <v>1.1273112</v>
+        <v>1.12081898</v>
       </c>
       <c r="P42">
-        <v>4.509244799999999</v>
+        <v>4.48327592</v>
       </c>
       <c r="Q42">
-        <v>6.899244799999999</v>
+        <v>6.873275919999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1249973298424917</v>
+        <v>0.1261645712550561</v>
       </c>
       <c r="T42">
-        <v>1.502344081888139</v>
+        <v>1.524486220162098</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.341008160536763</v>
+        <v>5.210739668816355</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09257549704048307</v>
+        <v>0.09245659617547114</v>
       </c>
       <c r="C43">
-        <v>37.6743859873603</v>
+        <v>37.22951521624513</v>
       </c>
       <c r="D43">
-        <v>55.7713859873603</v>
+        <v>55.91351521624514</v>
       </c>
       <c r="E43">
-        <v>-5.632999999999996</v>
+        <v>-5.045999999999996</v>
       </c>
       <c r="F43">
-        <v>24.067</v>
+        <v>24.654</v>
       </c>
       <c r="G43">
         <v>5.97</v>
@@ -4807,28 +4807,28 @@
         <v>6.935</v>
       </c>
       <c r="M43">
-        <v>1.3309051</v>
+        <v>1.3633662</v>
       </c>
       <c r="N43">
-        <v>5.6040949</v>
+        <v>5.571633799999999</v>
       </c>
       <c r="O43">
-        <v>1.12081898</v>
+        <v>1.11432676</v>
       </c>
       <c r="P43">
-        <v>4.48327592</v>
+        <v>4.457307039999999</v>
       </c>
       <c r="Q43">
-        <v>6.873275919999999</v>
+        <v>6.847307039999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1261645712550561</v>
+        <v>0.1273720623715019</v>
       </c>
       <c r="T43">
-        <v>1.524486220162098</v>
+        <v>1.547391880445505</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.210739668816355</v>
+        <v>5.086674438606442</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09245659617547111</v>
+        <v>0.0923376953104592</v>
       </c>
       <c r="C44">
-        <v>37.22951521624518</v>
+        <v>36.78537070749196</v>
       </c>
       <c r="D44">
-        <v>55.91351521624517</v>
+        <v>56.05637070749196</v>
       </c>
       <c r="E44">
-        <v>-5.045999999999999</v>
+        <v>-4.459</v>
       </c>
       <c r="F44">
-        <v>24.654</v>
+        <v>25.241</v>
       </c>
       <c r="G44">
         <v>5.97</v>
@@ -4889,28 +4889,28 @@
         <v>6.935</v>
       </c>
       <c r="M44">
-        <v>1.3633662</v>
+        <v>1.3958273</v>
       </c>
       <c r="N44">
-        <v>5.5716338</v>
+        <v>5.5391727</v>
       </c>
       <c r="O44">
-        <v>1.11432676</v>
+        <v>1.10783454</v>
       </c>
       <c r="P44">
-        <v>4.45730704</v>
+        <v>4.43133816</v>
       </c>
       <c r="Q44">
-        <v>6.84730704</v>
+        <v>6.82133816</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1273720623715019</v>
+        <v>0.1286219215972968</v>
       </c>
       <c r="T44">
-        <v>1.547391880445504</v>
+        <v>1.571101248107276</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.086674438606443</v>
+        <v>4.968379684220247</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0923376953104592</v>
+        <v>0.09221879444544724</v>
       </c>
       <c r="C45">
-        <v>36.78537070749196</v>
+        <v>36.34195804202268</v>
       </c>
       <c r="D45">
-        <v>56.05637070749196</v>
+        <v>56.19995804202269</v>
       </c>
       <c r="E45">
-        <v>-4.459</v>
+        <v>-3.871999999999996</v>
       </c>
       <c r="F45">
-        <v>25.241</v>
+        <v>25.828</v>
       </c>
       <c r="G45">
         <v>5.97</v>
@@ -4971,28 +4971,28 @@
         <v>6.935</v>
       </c>
       <c r="M45">
-        <v>1.3958273</v>
+        <v>1.4282884</v>
       </c>
       <c r="N45">
-        <v>5.5391727</v>
+        <v>5.506711599999999</v>
       </c>
       <c r="O45">
-        <v>1.10783454</v>
+        <v>1.10134232</v>
       </c>
       <c r="P45">
-        <v>4.43133816</v>
+        <v>4.405369279999999</v>
       </c>
       <c r="Q45">
-        <v>6.82133816</v>
+        <v>6.795369279999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1286219215972968</v>
+        <v>0.1299164186525844</v>
       </c>
       <c r="T45">
-        <v>1.571101248107276</v>
+        <v>1.595657378899825</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.968379684220247</v>
+        <v>4.855461964124331</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09221879444544724</v>
+        <v>0.0920998935804353</v>
       </c>
       <c r="C46">
-        <v>36.34195804202268</v>
+        <v>35.89928285808782</v>
       </c>
       <c r="D46">
-        <v>56.19995804202269</v>
+        <v>56.34428285808782</v>
       </c>
       <c r="E46">
-        <v>-3.871999999999996</v>
+        <v>-3.284999999999997</v>
       </c>
       <c r="F46">
-        <v>25.828</v>
+        <v>26.415</v>
       </c>
       <c r="G46">
         <v>5.97</v>
@@ -5053,28 +5053,28 @@
         <v>6.935</v>
       </c>
       <c r="M46">
-        <v>1.4282884</v>
+        <v>1.4607495</v>
       </c>
       <c r="N46">
-        <v>5.506711599999999</v>
+        <v>5.474250499999999</v>
       </c>
       <c r="O46">
-        <v>1.10134232</v>
+        <v>1.0948501</v>
       </c>
       <c r="P46">
-        <v>4.405369279999999</v>
+        <v>4.3794004</v>
       </c>
       <c r="Q46">
-        <v>6.795369279999999</v>
+        <v>6.769400399999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1299164186525844</v>
+        <v>0.1312579883280642</v>
       </c>
       <c r="T46">
-        <v>1.595657378899825</v>
+        <v>1.621106459903012</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.855461964124331</v>
+        <v>4.747562809366013</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0920998935804353</v>
+        <v>0.09198099271542334</v>
       </c>
       <c r="C47">
-        <v>35.89928285808782</v>
+        <v>35.45735085200444</v>
       </c>
       <c r="D47">
-        <v>56.34428285808782</v>
+        <v>56.48935085200444</v>
       </c>
       <c r="E47">
-        <v>-3.284999999999997</v>
+        <v>-2.697999999999997</v>
       </c>
       <c r="F47">
-        <v>26.415</v>
+        <v>27.002</v>
       </c>
       <c r="G47">
         <v>5.97</v>
@@ -5135,28 +5135,28 @@
         <v>6.935</v>
       </c>
       <c r="M47">
-        <v>1.4607495</v>
+        <v>1.4932106</v>
       </c>
       <c r="N47">
-        <v>5.474250499999999</v>
+        <v>5.441789399999999</v>
       </c>
       <c r="O47">
-        <v>1.0948501</v>
+        <v>1.08835788</v>
       </c>
       <c r="P47">
-        <v>4.3794004</v>
+        <v>4.353431519999999</v>
       </c>
       <c r="Q47">
-        <v>6.769400399999999</v>
+        <v>6.743431519999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1312579883280642</v>
+        <v>0.1326492457693025</v>
       </c>
       <c r="T47">
-        <v>1.621106459903012</v>
+        <v>1.647498099461872</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.747562809366013</v>
+        <v>4.644354922205881</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09198099271542334</v>
+        <v>0.0918620918504114</v>
       </c>
       <c r="C48">
-        <v>35.45735085200444</v>
+        <v>35.01616777890561</v>
       </c>
       <c r="D48">
-        <v>56.48935085200444</v>
+        <v>56.63516777890562</v>
       </c>
       <c r="E48">
-        <v>-2.697999999999997</v>
+        <v>-2.110999999999997</v>
       </c>
       <c r="F48">
-        <v>27.002</v>
+        <v>27.589</v>
       </c>
       <c r="G48">
         <v>5.97</v>
@@ -5217,28 +5217,28 @@
         <v>6.935</v>
       </c>
       <c r="M48">
-        <v>1.4932106</v>
+        <v>1.5256717</v>
       </c>
       <c r="N48">
-        <v>5.441789399999999</v>
+        <v>5.409328299999999</v>
       </c>
       <c r="O48">
-        <v>1.08835788</v>
+        <v>1.08186566</v>
       </c>
       <c r="P48">
-        <v>4.353431519999999</v>
+        <v>4.327462639999999</v>
       </c>
       <c r="Q48">
-        <v>6.743431519999999</v>
+        <v>6.717462639999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1326492457693025</v>
+        <v>0.1340930034913423</v>
       </c>
       <c r="T48">
-        <v>1.647498099461872</v>
+        <v>1.674885649947482</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.644354922205881</v>
+        <v>4.545538860031289</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0918620918504114</v>
+        <v>0.09270319098539946</v>
       </c>
       <c r="C49">
-        <v>35.01616777890561</v>
+        <v>33.41354838014082</v>
       </c>
       <c r="D49">
-        <v>56.63516777890562</v>
+        <v>55.61954838014083</v>
       </c>
       <c r="E49">
-        <v>-2.110999999999997</v>
+        <v>-1.523999999999997</v>
       </c>
       <c r="F49">
-        <v>27.589</v>
+        <v>28.176</v>
       </c>
       <c r="G49">
         <v>5.97</v>
@@ -5299,45 +5299,45 @@
         <v>6.935</v>
       </c>
       <c r="M49">
-        <v>1.5256717</v>
+        <v>1.6285728</v>
       </c>
       <c r="N49">
-        <v>5.409328299999999</v>
+        <v>5.3064272</v>
       </c>
       <c r="O49">
-        <v>1.08186566</v>
+        <v>1.06128544</v>
       </c>
       <c r="P49">
-        <v>4.327462639999999</v>
+        <v>4.24514176</v>
       </c>
       <c r="Q49">
-        <v>6.717462639999999</v>
+        <v>6.63514176</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1340930034913423</v>
+        <v>0.1355922903565374</v>
       </c>
       <c r="T49">
-        <v>1.674885649947482</v>
+        <v>1.703326567759462</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.545538860031289</v>
+        <v>4.258329747371441</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09270319098539946</v>
+        <v>0.0926042901203875</v>
       </c>
       <c r="C50">
-        <v>33.41354838014082</v>
+        <v>32.94407652621936</v>
       </c>
       <c r="D50">
-        <v>55.61954838014083</v>
+        <v>55.73707652621936</v>
       </c>
       <c r="E50">
-        <v>-1.523999999999997</v>
+        <v>-0.9369999999999976</v>
       </c>
       <c r="F50">
-        <v>28.176</v>
+        <v>28.763</v>
       </c>
       <c r="G50">
         <v>5.97</v>
@@ -5381,28 +5381,28 @@
         <v>6.935</v>
       </c>
       <c r="M50">
-        <v>1.6285728</v>
+        <v>1.6625014</v>
       </c>
       <c r="N50">
-        <v>5.3064272</v>
+        <v>5.2724986</v>
       </c>
       <c r="O50">
-        <v>1.06128544</v>
+        <v>1.05449972</v>
       </c>
       <c r="P50">
-        <v>4.24514176</v>
+        <v>4.21799888</v>
       </c>
       <c r="Q50">
-        <v>6.63514176</v>
+        <v>6.607998879999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1355922903565374</v>
+        <v>0.1371503727850735</v>
       </c>
       <c r="T50">
-        <v>1.703326567759462</v>
+        <v>1.732882815681715</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.258329747371441</v>
+        <v>4.171425058649573</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0926042901203875</v>
+        <v>0.09250538925537556</v>
       </c>
       <c r="C51">
-        <v>32.94407652621936</v>
+        <v>32.47510241508495</v>
       </c>
       <c r="D51">
-        <v>55.73707652621936</v>
+        <v>55.85510241508496</v>
       </c>
       <c r="E51">
-        <v>-0.9369999999999976</v>
+        <v>-0.3499999999999979</v>
       </c>
       <c r="F51">
-        <v>28.763</v>
+        <v>29.35</v>
       </c>
       <c r="G51">
         <v>5.97</v>
@@ -5463,28 +5463,28 @@
         <v>6.935</v>
       </c>
       <c r="M51">
-        <v>1.6625014</v>
+        <v>1.69643</v>
       </c>
       <c r="N51">
-        <v>5.2724986</v>
+        <v>5.238569999999999</v>
       </c>
       <c r="O51">
-        <v>1.05449972</v>
+        <v>1.047714</v>
       </c>
       <c r="P51">
-        <v>4.21799888</v>
+        <v>4.190855999999999</v>
       </c>
       <c r="Q51">
-        <v>6.607998879999999</v>
+        <v>6.580855999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1371503727850735</v>
+        <v>0.1387707785107511</v>
       </c>
       <c r="T51">
-        <v>1.732882815681715</v>
+        <v>1.763621313520859</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.171425058649573</v>
+        <v>4.087996557476583</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09250538925537556</v>
+        <v>0.09240648839036363</v>
       </c>
       <c r="C52">
-        <v>32.47510241508495</v>
+        <v>32.00662921542902</v>
       </c>
       <c r="D52">
-        <v>55.85510241508496</v>
+        <v>55.97362921542902</v>
       </c>
       <c r="E52">
-        <v>-0.3499999999999979</v>
+        <v>0.2370000000000019</v>
       </c>
       <c r="F52">
-        <v>29.35</v>
+        <v>29.937</v>
       </c>
       <c r="G52">
         <v>5.97</v>
@@ -5545,28 +5545,28 @@
         <v>6.935</v>
       </c>
       <c r="M52">
-        <v>1.69643</v>
+        <v>1.7303586</v>
       </c>
       <c r="N52">
-        <v>5.238569999999999</v>
+        <v>5.2046414</v>
       </c>
       <c r="O52">
-        <v>1.047714</v>
+        <v>1.04092828</v>
       </c>
       <c r="P52">
-        <v>4.190855999999999</v>
+        <v>4.16371312</v>
       </c>
       <c r="Q52">
-        <v>6.580855999999999</v>
+        <v>6.553713119999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1387707785107511</v>
+        <v>0.1404573232456401</v>
       </c>
       <c r="T52">
-        <v>1.763621313520859</v>
+        <v>1.795614443924866</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.087996557476583</v>
+        <v>4.007839762231944</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09240648839036363</v>
+        <v>0.09376358752535167</v>
       </c>
       <c r="C53">
-        <v>32.00662921542902</v>
+        <v>29.83589105676333</v>
       </c>
       <c r="D53">
-        <v>55.97362921542902</v>
+        <v>54.38989105676333</v>
       </c>
       <c r="E53">
-        <v>0.2370000000000019</v>
+        <v>0.8240000000000016</v>
       </c>
       <c r="F53">
-        <v>29.937</v>
+        <v>30.524</v>
       </c>
       <c r="G53">
         <v>5.97</v>
@@ -5627,45 +5627,45 @@
         <v>6.935</v>
       </c>
       <c r="M53">
-        <v>1.7303586</v>
+        <v>1.8711212</v>
       </c>
       <c r="N53">
-        <v>5.2046414</v>
+        <v>5.063878799999999</v>
       </c>
       <c r="O53">
-        <v>1.04092828</v>
+        <v>1.01277576</v>
       </c>
       <c r="P53">
-        <v>4.16371312</v>
+        <v>4.051103039999999</v>
       </c>
       <c r="Q53">
-        <v>6.553713119999999</v>
+        <v>6.441103039999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1404573232456401</v>
+        <v>0.142214140677816</v>
       </c>
       <c r="T53">
-        <v>1.795614443924866</v>
+        <v>1.828940621429039</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.007839762231944</v>
+        <v>3.706333934969044</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09376358752535167</v>
+        <v>0.09369268666033972</v>
       </c>
       <c r="C54">
-        <v>29.83589105676333</v>
+        <v>29.32941045529237</v>
       </c>
       <c r="D54">
-        <v>54.38989105676333</v>
+        <v>54.47041045529237</v>
       </c>
       <c r="E54">
-        <v>0.8240000000000016</v>
+        <v>1.411000000000005</v>
       </c>
       <c r="F54">
-        <v>30.524</v>
+        <v>31.111</v>
       </c>
       <c r="G54">
         <v>5.97</v>
@@ -5709,28 +5709,28 @@
         <v>6.935</v>
       </c>
       <c r="M54">
-        <v>1.8711212</v>
+        <v>1.9071043</v>
       </c>
       <c r="N54">
-        <v>5.063878799999999</v>
+        <v>5.027895699999999</v>
       </c>
       <c r="O54">
-        <v>1.01277576</v>
+        <v>1.00557914</v>
       </c>
       <c r="P54">
-        <v>4.051103039999999</v>
+        <v>4.022316559999999</v>
       </c>
       <c r="Q54">
-        <v>6.441103039999999</v>
+        <v>6.412316559999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.142214140677816</v>
+        <v>0.1440457162985952</v>
       </c>
       <c r="T54">
-        <v>1.828940621429039</v>
+        <v>1.863684934146156</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.706333934969044</v>
+        <v>3.636403106007363</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09369268666033972</v>
+        <v>0.09362178579532776</v>
       </c>
       <c r="C55">
-        <v>29.32941045529237</v>
+        <v>28.823168610903</v>
       </c>
       <c r="D55">
-        <v>54.47041045529237</v>
+        <v>54.55116861090301</v>
       </c>
       <c r="E55">
-        <v>1.411000000000005</v>
+        <v>1.998000000000005</v>
       </c>
       <c r="F55">
-        <v>31.111</v>
+        <v>31.698</v>
       </c>
       <c r="G55">
         <v>5.97</v>
@@ -5791,28 +5791,28 @@
         <v>6.935</v>
       </c>
       <c r="M55">
-        <v>1.9071043</v>
+        <v>1.9430874</v>
       </c>
       <c r="N55">
-        <v>5.027895699999999</v>
+        <v>4.991912599999999</v>
       </c>
       <c r="O55">
-        <v>1.00557914</v>
+        <v>0.9983825199999998</v>
       </c>
       <c r="P55">
-        <v>4.022316559999999</v>
+        <v>3.993530079999999</v>
       </c>
       <c r="Q55">
-        <v>6.412316559999999</v>
+        <v>6.383530079999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1440457162985952</v>
+        <v>0.1459569256420169</v>
       </c>
       <c r="T55">
-        <v>1.863684934146156</v>
+        <v>1.899939869155321</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.636403106007363</v>
+        <v>3.569062307747968</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09362178579532776</v>
+        <v>0.09355088493031583</v>
       </c>
       <c r="C56">
-        <v>28.823168610903</v>
+        <v>28.31716658711996</v>
       </c>
       <c r="D56">
-        <v>54.55116861090301</v>
+        <v>54.63216658711997</v>
       </c>
       <c r="E56">
-        <v>1.998000000000005</v>
+        <v>2.585000000000004</v>
       </c>
       <c r="F56">
-        <v>31.698</v>
+        <v>32.285</v>
       </c>
       <c r="G56">
         <v>5.97</v>
@@ -5873,28 +5873,28 @@
         <v>6.935</v>
       </c>
       <c r="M56">
-        <v>1.9430874</v>
+        <v>1.9790705</v>
       </c>
       <c r="N56">
-        <v>4.991912599999999</v>
+        <v>4.9559295</v>
       </c>
       <c r="O56">
-        <v>0.9983825199999998</v>
+        <v>0.9911859000000001</v>
       </c>
       <c r="P56">
-        <v>3.993530079999999</v>
+        <v>3.9647436</v>
       </c>
       <c r="Q56">
-        <v>6.383530079999999</v>
+        <v>6.354743599999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1459569256420169</v>
+        <v>0.1479530776229241</v>
       </c>
       <c r="T56">
-        <v>1.899939869155321</v>
+        <v>1.937806134609339</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.569062307747968</v>
+        <v>3.504170265788914</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09355088493031583</v>
+        <v>0.09473438406530388</v>
       </c>
       <c r="C57">
-        <v>28.31716658711996</v>
+        <v>26.40886413009724</v>
       </c>
       <c r="D57">
-        <v>54.63216658711997</v>
+        <v>53.31086413009724</v>
       </c>
       <c r="E57">
-        <v>2.585000000000004</v>
+        <v>3.172000000000008</v>
       </c>
       <c r="F57">
-        <v>32.285</v>
+        <v>32.87200000000001</v>
       </c>
       <c r="G57">
         <v>5.97</v>
@@ -5955,45 +5955,45 @@
         <v>6.935</v>
       </c>
       <c r="M57">
-        <v>1.9790705</v>
+        <v>2.107095200000001</v>
       </c>
       <c r="N57">
-        <v>4.9559295</v>
+        <v>4.827904799999999</v>
       </c>
       <c r="O57">
-        <v>0.9911859000000001</v>
+        <v>0.9655809599999998</v>
       </c>
       <c r="P57">
-        <v>3.9647436</v>
+        <v>3.862323839999999</v>
       </c>
       <c r="Q57">
-        <v>6.354743599999999</v>
+        <v>6.252323839999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1479530776229241</v>
+        <v>0.1500399637847816</v>
       </c>
       <c r="T57">
-        <v>1.937806134609339</v>
+        <v>1.97739359394763</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.504170265788914</v>
+        <v>3.291260878957912</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09473438406530388</v>
+        <v>0.09468588320029195</v>
       </c>
       <c r="C58">
-        <v>26.40886413009724</v>
+        <v>25.8747551255253</v>
       </c>
       <c r="D58">
-        <v>53.31086413009724</v>
+        <v>53.3637551255253</v>
       </c>
       <c r="E58">
-        <v>3.172000000000008</v>
+        <v>3.759000000000004</v>
       </c>
       <c r="F58">
-        <v>32.87200000000001</v>
+        <v>33.459</v>
       </c>
       <c r="G58">
         <v>5.97</v>
@@ -6037,28 +6037,28 @@
         <v>6.935</v>
       </c>
       <c r="M58">
-        <v>2.107095200000001</v>
+        <v>2.1447219</v>
       </c>
       <c r="N58">
-        <v>4.827904799999999</v>
+        <v>4.790278099999999</v>
       </c>
       <c r="O58">
-        <v>0.9655809599999998</v>
+        <v>0.9580556199999999</v>
       </c>
       <c r="P58">
-        <v>3.862323839999999</v>
+        <v>3.83222248</v>
       </c>
       <c r="Q58">
-        <v>6.252323839999999</v>
+        <v>6.222222479999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1500399637847816</v>
+        <v>0.1522239144192836</v>
       </c>
       <c r="T58">
-        <v>1.97739359394763</v>
+        <v>2.018822330464446</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.291260878957912</v>
+        <v>3.233519460028826</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09468588320029195</v>
+        <v>0.09463738233527999</v>
       </c>
       <c r="C59">
-        <v>25.8747551255253</v>
+        <v>25.34075117404619</v>
       </c>
       <c r="D59">
-        <v>53.3637551255253</v>
+        <v>53.4167511740462</v>
       </c>
       <c r="E59">
-        <v>3.759000000000004</v>
+        <v>4.346000000000007</v>
       </c>
       <c r="F59">
-        <v>33.459</v>
+        <v>34.04600000000001</v>
       </c>
       <c r="G59">
         <v>5.97</v>
@@ -6119,28 +6119,28 @@
         <v>6.935</v>
       </c>
       <c r="M59">
-        <v>2.1447219</v>
+        <v>2.182348600000001</v>
       </c>
       <c r="N59">
-        <v>4.790278099999999</v>
+        <v>4.7526514</v>
       </c>
       <c r="O59">
-        <v>0.9580556199999999</v>
+        <v>0.9505302799999999</v>
       </c>
       <c r="P59">
-        <v>3.83222248</v>
+        <v>3.80212112</v>
       </c>
       <c r="Q59">
-        <v>6.222222479999999</v>
+        <v>6.192121119999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1522239144192836</v>
+        <v>0.1545118627030476</v>
       </c>
       <c r="T59">
-        <v>2.018822330464446</v>
+        <v>2.062223863958253</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.233519460028826</v>
+        <v>3.177769124511088</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09463738233527999</v>
+        <v>0.09458888147026806</v>
       </c>
       <c r="C60">
-        <v>25.3407511740462</v>
+        <v>24.80685258895867</v>
       </c>
       <c r="D60">
-        <v>53.4167511740462</v>
+        <v>53.46985258895867</v>
       </c>
       <c r="E60">
-        <v>4.346</v>
+        <v>4.933000000000003</v>
       </c>
       <c r="F60">
-        <v>34.046</v>
+        <v>34.633</v>
       </c>
       <c r="G60">
         <v>5.97</v>
@@ -6201,28 +6201,28 @@
         <v>6.935</v>
       </c>
       <c r="M60">
-        <v>2.1823486</v>
+        <v>2.2199753</v>
       </c>
       <c r="N60">
-        <v>4.7526514</v>
+        <v>4.715024699999999</v>
       </c>
       <c r="O60">
-        <v>0.9505302799999999</v>
+        <v>0.9430049399999998</v>
       </c>
       <c r="P60">
-        <v>3.80212112</v>
+        <v>3.772019759999999</v>
       </c>
       <c r="Q60">
-        <v>6.192121119999999</v>
+        <v>6.162019759999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1545118627030476</v>
+        <v>0.156911418220166</v>
       </c>
       <c r="T60">
-        <v>2.062223863958252</v>
+        <v>2.107742545427368</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.177769124511088</v>
+        <v>3.123908630875307</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09458888147026806</v>
+        <v>0.09454038060525612</v>
       </c>
       <c r="C61">
-        <v>24.80685258895867</v>
+        <v>24.2730596848086</v>
       </c>
       <c r="D61">
-        <v>53.46985258895867</v>
+        <v>53.5230596848086</v>
       </c>
       <c r="E61">
-        <v>4.933000000000003</v>
+        <v>5.52</v>
       </c>
       <c r="F61">
-        <v>34.633</v>
+        <v>35.22</v>
       </c>
       <c r="G61">
         <v>5.97</v>
@@ -6283,28 +6283,28 @@
         <v>6.935</v>
       </c>
       <c r="M61">
-        <v>2.2199753</v>
+        <v>2.257602</v>
       </c>
       <c r="N61">
-        <v>4.715024699999999</v>
+        <v>4.677398</v>
       </c>
       <c r="O61">
-        <v>0.9430049399999998</v>
+        <v>0.9354796000000001</v>
       </c>
       <c r="P61">
-        <v>3.772019759999999</v>
+        <v>3.7419184</v>
       </c>
       <c r="Q61">
-        <v>6.162019759999999</v>
+        <v>6.1319184</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.156911418220166</v>
+        <v>0.1594309515131403</v>
       </c>
       <c r="T61">
-        <v>2.107742545427368</v>
+        <v>2.155537160969939</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.123908630875307</v>
+        <v>3.071843487027386</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09454038060525612</v>
+        <v>0.09449187974024417</v>
       </c>
       <c r="C62">
-        <v>24.2730596848086</v>
+        <v>23.73937277739503</v>
       </c>
       <c r="D62">
-        <v>53.5230596848086</v>
+        <v>53.57637277739503</v>
       </c>
       <c r="E62">
-        <v>5.52</v>
+        <v>6.107000000000003</v>
       </c>
       <c r="F62">
-        <v>35.22</v>
+        <v>35.807</v>
       </c>
       <c r="G62">
         <v>5.97</v>
@@ -6365,28 +6365,28 @@
         <v>6.935</v>
       </c>
       <c r="M62">
-        <v>2.257602</v>
+        <v>2.2952287</v>
       </c>
       <c r="N62">
-        <v>4.677398</v>
+        <v>4.6397713</v>
       </c>
       <c r="O62">
-        <v>0.9354796000000001</v>
+        <v>0.9279542599999999</v>
       </c>
       <c r="P62">
-        <v>3.7419184</v>
+        <v>3.71181704</v>
       </c>
       <c r="Q62">
-        <v>6.1319184</v>
+        <v>6.101817039999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1594309515131403</v>
+        <v>0.1620796916416517</v>
       </c>
       <c r="T62">
-        <v>2.155537160969939</v>
+        <v>2.205782782437769</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.071843487027386</v>
+        <v>3.021485397076117</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09449187974024417</v>
+        <v>0.09831217887523222</v>
       </c>
       <c r="C63">
-        <v>23.73937277739503</v>
+        <v>19.25465276346095</v>
       </c>
       <c r="D63">
-        <v>53.57637277739503</v>
+        <v>49.67865276346095</v>
       </c>
       <c r="E63">
-        <v>6.107000000000003</v>
+        <v>6.693999999999999</v>
       </c>
       <c r="F63">
-        <v>35.807</v>
+        <v>36.394</v>
       </c>
       <c r="G63">
         <v>5.97</v>
@@ -6447,45 +6447,45 @@
         <v>6.935</v>
       </c>
       <c r="M63">
-        <v>2.2952287</v>
+        <v>2.6167286</v>
       </c>
       <c r="N63">
-        <v>4.6397713</v>
+        <v>4.3182714</v>
       </c>
       <c r="O63">
-        <v>0.9279542599999999</v>
+        <v>0.86365428</v>
       </c>
       <c r="P63">
-        <v>3.71181704</v>
+        <v>3.45461712</v>
       </c>
       <c r="Q63">
-        <v>6.101817039999999</v>
+        <v>5.844617119999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1620796916416517</v>
+        <v>0.1648678391453479</v>
       </c>
       <c r="T63">
-        <v>2.205782782437769</v>
+        <v>2.258672910298644</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.021485397076117</v>
+        <v>2.650255742991459</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09831217887523222</v>
+        <v>0.09832607801022028</v>
       </c>
       <c r="C64">
-        <v>19.25465276346095</v>
+        <v>18.6545070970236</v>
       </c>
       <c r="D64">
-        <v>49.67865276346095</v>
+        <v>49.6655070970236</v>
       </c>
       <c r="E64">
-        <v>6.693999999999999</v>
+        <v>7.281000000000002</v>
       </c>
       <c r="F64">
-        <v>36.394</v>
+        <v>36.981</v>
       </c>
       <c r="G64">
         <v>5.97</v>
@@ -6529,28 +6529,28 @@
         <v>6.935</v>
       </c>
       <c r="M64">
-        <v>2.6167286</v>
+        <v>2.658933900000001</v>
       </c>
       <c r="N64">
-        <v>4.3182714</v>
+        <v>4.2760661</v>
       </c>
       <c r="O64">
-        <v>0.86365428</v>
+        <v>0.85521322</v>
       </c>
       <c r="P64">
-        <v>3.45461712</v>
+        <v>3.42085288</v>
       </c>
       <c r="Q64">
-        <v>5.844617119999999</v>
+        <v>5.810852879999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1648678391453479</v>
+        <v>0.1678066973249197</v>
       </c>
       <c r="T64">
-        <v>2.258672910298644</v>
+        <v>2.314421963989836</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.650255742991459</v>
+        <v>2.608188191515404</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09832607801022028</v>
+        <v>0.09833997714520834</v>
       </c>
       <c r="C65">
-        <v>18.6545070970236</v>
+        <v>18.05436838580025</v>
       </c>
       <c r="D65">
-        <v>49.6655070970236</v>
+        <v>49.65236838580026</v>
       </c>
       <c r="E65">
-        <v>7.281000000000002</v>
+        <v>7.868000000000006</v>
       </c>
       <c r="F65">
-        <v>36.981</v>
+        <v>37.568</v>
       </c>
       <c r="G65">
         <v>5.97</v>
@@ -6611,28 +6611,28 @@
         <v>6.935</v>
       </c>
       <c r="M65">
-        <v>2.658933900000001</v>
+        <v>2.701139200000001</v>
       </c>
       <c r="N65">
-        <v>4.2760661</v>
+        <v>4.233860799999999</v>
       </c>
       <c r="O65">
-        <v>0.85521322</v>
+        <v>0.8467721599999998</v>
       </c>
       <c r="P65">
-        <v>3.42085288</v>
+        <v>3.387088639999999</v>
       </c>
       <c r="Q65">
-        <v>5.810852879999999</v>
+        <v>5.777088639999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1678066973249197</v>
+        <v>0.1709088254033565</v>
       </c>
       <c r="T65">
-        <v>2.314421963989836</v>
+        <v>2.373268187330539</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.608188191515404</v>
+        <v>2.567435251022975</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09833997714520834</v>
+        <v>0.09835387628019639</v>
       </c>
       <c r="C66">
-        <v>18.05436838580025</v>
+        <v>17.4542366242725</v>
       </c>
       <c r="D66">
-        <v>49.65236838580026</v>
+        <v>49.63923662427251</v>
       </c>
       <c r="E66">
-        <v>7.868000000000006</v>
+        <v>8.455000000000002</v>
       </c>
       <c r="F66">
-        <v>37.568</v>
+        <v>38.155</v>
       </c>
       <c r="G66">
         <v>5.97</v>
@@ -6693,28 +6693,28 @@
         <v>6.935</v>
       </c>
       <c r="M66">
-        <v>2.701139200000001</v>
+        <v>2.7433445</v>
       </c>
       <c r="N66">
-        <v>4.233860799999999</v>
+        <v>4.1916555</v>
       </c>
       <c r="O66">
-        <v>0.8467721599999998</v>
+        <v>0.8383311</v>
       </c>
       <c r="P66">
-        <v>3.387088639999999</v>
+        <v>3.3533244</v>
       </c>
       <c r="Q66">
-        <v>5.777088639999999</v>
+        <v>5.743324399999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1709088254033565</v>
+        <v>0.1741882179434182</v>
       </c>
       <c r="T66">
-        <v>2.373268187330539</v>
+        <v>2.435477052004996</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.567435251022975</v>
+        <v>2.527936247161084</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09835387628019639</v>
+        <v>0.1004269754151844</v>
       </c>
       <c r="C67">
-        <v>17.4542366242725</v>
+        <v>14.98342267109064</v>
       </c>
       <c r="D67">
-        <v>49.63923662427251</v>
+        <v>47.75542267109065</v>
       </c>
       <c r="E67">
-        <v>8.455000000000002</v>
+        <v>9.042000000000005</v>
       </c>
       <c r="F67">
-        <v>38.155</v>
+        <v>38.742</v>
       </c>
       <c r="G67">
         <v>5.97</v>
@@ -6775,45 +6775,45 @@
         <v>6.935</v>
       </c>
       <c r="M67">
-        <v>2.7433445</v>
+        <v>2.9366436</v>
       </c>
       <c r="N67">
-        <v>4.1916555</v>
+        <v>3.998356399999999</v>
       </c>
       <c r="O67">
-        <v>0.8383311</v>
+        <v>0.7996712799999999</v>
       </c>
       <c r="P67">
-        <v>3.3533244</v>
+        <v>3.198685119999999</v>
       </c>
       <c r="Q67">
-        <v>5.743324399999999</v>
+        <v>5.588685119999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1741882179434182</v>
+        <v>0.1776605159270131</v>
       </c>
       <c r="T67">
-        <v>2.435477052004996</v>
+        <v>2.501345261660303</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.527936247161084</v>
+        <v>2.361539548074543</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1004269754151844</v>
+        <v>0.1004720745501725</v>
       </c>
       <c r="C68">
-        <v>14.98342267109064</v>
+        <v>14.35702910003675</v>
       </c>
       <c r="D68">
-        <v>47.75542267109065</v>
+        <v>47.71602910003676</v>
       </c>
       <c r="E68">
-        <v>9.042000000000005</v>
+        <v>9.629000000000008</v>
       </c>
       <c r="F68">
-        <v>38.742</v>
+        <v>39.32900000000001</v>
       </c>
       <c r="G68">
         <v>5.97</v>
@@ -6857,28 +6857,28 @@
         <v>6.935</v>
       </c>
       <c r="M68">
-        <v>2.9366436</v>
+        <v>2.981138200000001</v>
       </c>
       <c r="N68">
-        <v>3.998356399999999</v>
+        <v>3.953861799999999</v>
       </c>
       <c r="O68">
-        <v>0.7996712799999999</v>
+        <v>0.7907723599999998</v>
       </c>
       <c r="P68">
-        <v>3.198685119999999</v>
+        <v>3.163089439999999</v>
       </c>
       <c r="Q68">
-        <v>5.588685119999999</v>
+        <v>5.553089439999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1776605159270131</v>
+        <v>0.1813432562126439</v>
       </c>
       <c r="T68">
-        <v>2.501345261660303</v>
+        <v>2.571205484021994</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.361539548074543</v>
+        <v>2.326292689148057</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1004720745501725</v>
+        <v>0.1005171736851606</v>
       </c>
       <c r="C69">
-        <v>14.35702910003675</v>
+        <v>13.73070046713151</v>
       </c>
       <c r="D69">
-        <v>47.71602910003676</v>
+        <v>47.67670046713152</v>
       </c>
       <c r="E69">
-        <v>9.629000000000008</v>
+        <v>10.216</v>
       </c>
       <c r="F69">
-        <v>39.32900000000001</v>
+        <v>39.916</v>
       </c>
       <c r="G69">
         <v>5.97</v>
@@ -6939,28 +6939,28 @@
         <v>6.935</v>
       </c>
       <c r="M69">
-        <v>2.981138200000001</v>
+        <v>3.0256328</v>
       </c>
       <c r="N69">
-        <v>3.953861799999999</v>
+        <v>3.909367199999999</v>
       </c>
       <c r="O69">
-        <v>0.7907723599999998</v>
+        <v>0.7818734399999999</v>
       </c>
       <c r="P69">
-        <v>3.163089439999999</v>
+        <v>3.127493759999999</v>
       </c>
       <c r="Q69">
-        <v>5.553089439999999</v>
+        <v>5.517493759999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1813432562126439</v>
+        <v>0.1852561677661267</v>
       </c>
       <c r="T69">
-        <v>2.571205484021994</v>
+        <v>2.645431970281289</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.326292689148057</v>
+        <v>2.292082502542939</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1005171736851606</v>
+        <v>0.1005622728201486</v>
       </c>
       <c r="C70">
-        <v>13.73070046713151</v>
+        <v>13.10443661193665</v>
       </c>
       <c r="D70">
-        <v>47.67670046713152</v>
+        <v>47.63743661193666</v>
       </c>
       <c r="E70">
-        <v>10.216</v>
+        <v>10.80300000000001</v>
       </c>
       <c r="F70">
-        <v>39.916</v>
+        <v>40.50300000000001</v>
       </c>
       <c r="G70">
         <v>5.97</v>
@@ -7021,28 +7021,28 @@
         <v>6.935</v>
       </c>
       <c r="M70">
-        <v>3.0256328</v>
+        <v>3.070127400000001</v>
       </c>
       <c r="N70">
-        <v>3.909367199999999</v>
+        <v>3.864872599999999</v>
       </c>
       <c r="O70">
-        <v>0.7818734399999999</v>
+        <v>0.7729745199999998</v>
       </c>
       <c r="P70">
-        <v>3.127493759999999</v>
+        <v>3.091898079999999</v>
       </c>
       <c r="Q70">
-        <v>5.517493759999999</v>
+        <v>5.481898079999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1852561677661267</v>
+        <v>0.1894215252262858</v>
       </c>
       <c r="T70">
-        <v>2.645431970281289</v>
+        <v>2.7244472621057</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.292082502542939</v>
+        <v>2.258863915549562</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1005622728201486</v>
+        <v>0.1006073719551367</v>
       </c>
       <c r="C71">
-        <v>13.10443661193665</v>
+        <v>12.478237374542</v>
       </c>
       <c r="D71">
-        <v>47.63743661193666</v>
+        <v>47.598237374542</v>
       </c>
       <c r="E71">
-        <v>10.80300000000001</v>
+        <v>11.39</v>
       </c>
       <c r="F71">
-        <v>40.50300000000001</v>
+        <v>41.09</v>
       </c>
       <c r="G71">
         <v>5.97</v>
@@ -7103,28 +7103,28 @@
         <v>6.935</v>
       </c>
       <c r="M71">
-        <v>3.070127400000001</v>
+        <v>3.114622000000001</v>
       </c>
       <c r="N71">
-        <v>3.864872599999999</v>
+        <v>3.820377999999999</v>
       </c>
       <c r="O71">
-        <v>0.7729745199999998</v>
+        <v>0.7640755999999999</v>
       </c>
       <c r="P71">
-        <v>3.091898079999999</v>
+        <v>3.056302399999999</v>
       </c>
       <c r="Q71">
-        <v>5.481898079999999</v>
+        <v>5.446302399999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1894215252262858</v>
+        <v>0.1938645731837889</v>
       </c>
       <c r="T71">
-        <v>2.7244472621057</v>
+        <v>2.808730240051739</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.258863915549562</v>
+        <v>2.226594431041712</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1006073719551367</v>
+        <v>0.1006524710901247</v>
       </c>
       <c r="C72">
-        <v>12.478237374542</v>
+        <v>11.85210259556327</v>
       </c>
       <c r="D72">
-        <v>47.598237374542</v>
+        <v>47.55910259556328</v>
       </c>
       <c r="E72">
-        <v>11.39</v>
+        <v>11.97700000000001</v>
       </c>
       <c r="F72">
-        <v>41.09</v>
+        <v>41.67700000000001</v>
       </c>
       <c r="G72">
         <v>5.97</v>
@@ -7185,28 +7185,28 @@
         <v>6.935</v>
       </c>
       <c r="M72">
-        <v>3.114622000000001</v>
+        <v>3.159116600000001</v>
       </c>
       <c r="N72">
-        <v>3.820377999999999</v>
+        <v>3.775883399999999</v>
       </c>
       <c r="O72">
-        <v>0.7640755999999999</v>
+        <v>0.7551766799999998</v>
       </c>
       <c r="P72">
-        <v>3.056302399999999</v>
+        <v>3.020706719999999</v>
       </c>
       <c r="Q72">
-        <v>5.446302399999999</v>
+        <v>5.410706719999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1938645731837889</v>
+        <v>0.1986140382418094</v>
       </c>
       <c r="T72">
-        <v>2.808730240051739</v>
+        <v>2.89882583716647</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.226594431041712</v>
+        <v>2.195233946097462</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1006524710901247</v>
+        <v>0.1006975702251128</v>
       </c>
       <c r="C73">
-        <v>11.8521025955633</v>
+        <v>11.22603211614002</v>
       </c>
       <c r="D73">
-        <v>47.5591025955633</v>
+        <v>47.52003211614002</v>
       </c>
       <c r="E73">
-        <v>11.977</v>
+        <v>12.564</v>
       </c>
       <c r="F73">
-        <v>41.677</v>
+        <v>42.264</v>
       </c>
       <c r="G73">
         <v>5.97</v>
@@ -7267,28 +7267,28 @@
         <v>6.935</v>
       </c>
       <c r="M73">
-        <v>3.1591166</v>
+        <v>3.203611200000001</v>
       </c>
       <c r="N73">
-        <v>3.775883399999999</v>
+        <v>3.731388799999999</v>
       </c>
       <c r="O73">
-        <v>0.7551766799999999</v>
+        <v>0.7462777599999999</v>
       </c>
       <c r="P73">
-        <v>3.020706719999999</v>
+        <v>2.985111039999999</v>
       </c>
       <c r="Q73">
-        <v>5.410706719999999</v>
+        <v>5.375111039999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1986140382418093</v>
+        <v>0.2037027508039741</v>
       </c>
       <c r="T73">
-        <v>2.898825837166469</v>
+        <v>2.995356834075109</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.195233946097463</v>
+        <v>2.164744585734998</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1006975702251128</v>
+        <v>0.1007426693601008</v>
       </c>
       <c r="C74">
-        <v>11.22603211614002</v>
+        <v>10.60002577793325</v>
       </c>
       <c r="D74">
-        <v>47.52003211614002</v>
+        <v>47.48102577793325</v>
       </c>
       <c r="E74">
-        <v>12.564</v>
+        <v>13.151</v>
       </c>
       <c r="F74">
-        <v>42.264</v>
+        <v>42.851</v>
       </c>
       <c r="G74">
         <v>5.97</v>
@@ -7349,28 +7349,28 @@
         <v>6.935</v>
       </c>
       <c r="M74">
-        <v>3.203611200000001</v>
+        <v>3.2481058</v>
       </c>
       <c r="N74">
-        <v>3.731388799999999</v>
+        <v>3.686894199999999</v>
       </c>
       <c r="O74">
-        <v>0.7462777599999999</v>
+        <v>0.7373788399999999</v>
       </c>
       <c r="P74">
-        <v>2.985111039999999</v>
+        <v>2.949515359999999</v>
       </c>
       <c r="Q74">
-        <v>5.375111039999998</v>
+        <v>5.339515359999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2037027508039741</v>
+        <v>0.2091684050374104</v>
       </c>
       <c r="T74">
-        <v>2.995356834075109</v>
+        <v>3.099038275199204</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.164744585734998</v>
+        <v>2.13509055031397</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1007426693601008</v>
+        <v>0.1007877684950889</v>
       </c>
       <c r="C75">
-        <v>10.60002577793325</v>
+        <v>9.974083423123538</v>
       </c>
       <c r="D75">
-        <v>47.48102577793325</v>
+        <v>47.44208342312354</v>
       </c>
       <c r="E75">
-        <v>13.151</v>
+        <v>13.738</v>
       </c>
       <c r="F75">
-        <v>42.851</v>
+        <v>43.438</v>
       </c>
       <c r="G75">
         <v>5.97</v>
@@ -7431,28 +7431,28 @@
         <v>6.935</v>
       </c>
       <c r="M75">
-        <v>3.2481058</v>
+        <v>3.2926004</v>
       </c>
       <c r="N75">
-        <v>3.686894199999999</v>
+        <v>3.642399599999999</v>
       </c>
       <c r="O75">
-        <v>0.7373788399999999</v>
+        <v>0.7284799199999998</v>
       </c>
       <c r="P75">
-        <v>2.949515359999999</v>
+        <v>2.913919679999999</v>
       </c>
       <c r="Q75">
-        <v>5.339515359999999</v>
+        <v>5.303919679999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2091684050374104</v>
+        <v>0.2150544942118802</v>
       </c>
       <c r="T75">
-        <v>3.099038275199204</v>
+        <v>3.210695211794384</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.13509055031397</v>
+        <v>2.106237975309727</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1007877684950889</v>
+        <v>0.1008328676300769</v>
       </c>
       <c r="C76">
-        <v>9.974083423123538</v>
+        <v>9.348204894408731</v>
       </c>
       <c r="D76">
-        <v>47.44208342312354</v>
+        <v>47.40320489440874</v>
       </c>
       <c r="E76">
-        <v>13.738</v>
+        <v>14.32500000000001</v>
       </c>
       <c r="F76">
-        <v>43.438</v>
+        <v>44.02500000000001</v>
       </c>
       <c r="G76">
         <v>5.97</v>
@@ -7513,28 +7513,28 @@
         <v>6.935</v>
       </c>
       <c r="M76">
-        <v>3.2926004</v>
+        <v>3.337095000000001</v>
       </c>
       <c r="N76">
-        <v>3.642399599999999</v>
+        <v>3.597904999999999</v>
       </c>
       <c r="O76">
-        <v>0.7284799199999998</v>
+        <v>0.7195809999999998</v>
       </c>
       <c r="P76">
-        <v>2.913919679999999</v>
+        <v>2.878323999999999</v>
       </c>
       <c r="Q76">
-        <v>5.303919679999999</v>
+        <v>5.268323999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2150544942118802</v>
+        <v>0.2214114705203077</v>
       </c>
       <c r="T76">
-        <v>3.210695211794384</v>
+        <v>3.331284703317178</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.106237975309727</v>
+        <v>2.078154802305598</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1008328676300769</v>
+        <v>0.100877966765065</v>
       </c>
       <c r="C77">
-        <v>9.348204894408731</v>
+        <v>8.722390035001915</v>
       </c>
       <c r="D77">
-        <v>47.40320489440874</v>
+        <v>47.36439003500192</v>
       </c>
       <c r="E77">
-        <v>14.32500000000001</v>
+        <v>14.912</v>
       </c>
       <c r="F77">
-        <v>44.02500000000001</v>
+        <v>44.612</v>
       </c>
       <c r="G77">
         <v>5.97</v>
@@ -7595,28 +7595,28 @@
         <v>6.935</v>
       </c>
       <c r="M77">
-        <v>3.337095000000001</v>
+        <v>3.3815896</v>
       </c>
       <c r="N77">
-        <v>3.597904999999999</v>
+        <v>3.553410399999999</v>
       </c>
       <c r="O77">
-        <v>0.7195809999999998</v>
+        <v>0.7106820799999999</v>
       </c>
       <c r="P77">
-        <v>2.878323999999999</v>
+        <v>2.84272832</v>
       </c>
       <c r="Q77">
-        <v>5.268323999999999</v>
+        <v>5.23272832</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2214114705203077</v>
+        <v>0.2282981948544374</v>
       </c>
       <c r="T77">
-        <v>3.331284703317178</v>
+        <v>3.461923319133538</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.078154802305598</v>
+        <v>2.050810660169998</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.100877966765065</v>
+        <v>0.100923065900053</v>
       </c>
       <c r="C78">
-        <v>8.722390035001915</v>
+        <v>8.096638688629263</v>
       </c>
       <c r="D78">
-        <v>47.36439003500192</v>
+        <v>47.32563868862927</v>
       </c>
       <c r="E78">
-        <v>14.912</v>
+        <v>15.49900000000001</v>
       </c>
       <c r="F78">
-        <v>44.612</v>
+        <v>45.19900000000001</v>
       </c>
       <c r="G78">
         <v>5.97</v>
@@ -7677,28 +7677,28 @@
         <v>6.935</v>
       </c>
       <c r="M78">
-        <v>3.3815896</v>
+        <v>3.4260842</v>
       </c>
       <c r="N78">
-        <v>3.553410399999999</v>
+        <v>3.508915799999999</v>
       </c>
       <c r="O78">
-        <v>0.7106820799999999</v>
+        <v>0.7017831599999999</v>
       </c>
       <c r="P78">
-        <v>2.84272832</v>
+        <v>2.807132639999999</v>
       </c>
       <c r="Q78">
-        <v>5.23272832</v>
+        <v>5.19713264</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2282981948544374</v>
+        <v>0.2357837647828393</v>
       </c>
       <c r="T78">
-        <v>3.461923319133538</v>
+        <v>3.603921814586103</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.050810660169998</v>
+        <v>2.024176755492465</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.100923065900053</v>
+        <v>0.1098289650350411</v>
       </c>
       <c r="C79">
-        <v>8.096638688629263</v>
+        <v>0.9270340123056897</v>
       </c>
       <c r="D79">
-        <v>47.32563868862927</v>
+        <v>40.74303401230569</v>
       </c>
       <c r="E79">
-        <v>15.49900000000001</v>
+        <v>16.086</v>
       </c>
       <c r="F79">
-        <v>45.19900000000001</v>
+        <v>45.786</v>
       </c>
       <c r="G79">
         <v>5.97</v>
@@ -7759,45 +7759,45 @@
         <v>6.935</v>
       </c>
       <c r="M79">
-        <v>3.4260842</v>
+        <v>4.12074</v>
       </c>
       <c r="N79">
-        <v>3.508915799999999</v>
+        <v>2.81426</v>
       </c>
       <c r="O79">
-        <v>0.7017831599999999</v>
+        <v>0.562852</v>
       </c>
       <c r="P79">
-        <v>2.807132639999999</v>
+        <v>2.251408</v>
       </c>
       <c r="Q79">
-        <v>5.19713264</v>
+        <v>4.641408</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2357837647828393</v>
+        <v>0.2439498410683686</v>
       </c>
       <c r="T79">
-        <v>3.603921814586103</v>
+        <v>3.758829264170719</v>
       </c>
       <c r="U79">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
         <v>0.2</v>
       </c>
       <c r="W79">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.024176755492465</v>
+        <v>1.682950149730388</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1098289650350411</v>
+        <v>0.1099876641700291</v>
       </c>
       <c r="C80">
-        <v>0.9270340123056897</v>
+        <v>0.2392999485545175</v>
       </c>
       <c r="D80">
-        <v>40.74303401230569</v>
+        <v>40.64229994855452</v>
       </c>
       <c r="E80">
-        <v>16.086</v>
+        <v>16.67300000000001</v>
       </c>
       <c r="F80">
-        <v>45.786</v>
+        <v>46.373</v>
       </c>
       <c r="G80">
         <v>5.97</v>
@@ -7841,28 +7841,28 @@
         <v>6.935</v>
       </c>
       <c r="M80">
-        <v>4.12074</v>
+        <v>4.173570000000001</v>
       </c>
       <c r="N80">
-        <v>2.81426</v>
+        <v>2.761429999999999</v>
       </c>
       <c r="O80">
-        <v>0.562852</v>
+        <v>0.5522859999999998</v>
       </c>
       <c r="P80">
-        <v>2.251408</v>
+        <v>2.209143999999999</v>
       </c>
       <c r="Q80">
-        <v>4.641408</v>
+        <v>4.599143999999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2439498410683686</v>
+        <v>0.2528936389049007</v>
       </c>
       <c r="T80">
-        <v>3.758829264170719</v>
+        <v>3.928489804191967</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.682950149730388</v>
+        <v>1.661646983278104</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1099876641700291</v>
+        <v>0.1101463633050172</v>
       </c>
       <c r="C81">
-        <v>0.2392999485545175</v>
+        <v>-0.4479372290336983</v>
       </c>
       <c r="D81">
-        <v>40.64229994855452</v>
+        <v>40.54206277096631</v>
       </c>
       <c r="E81">
-        <v>16.67300000000001</v>
+        <v>17.26000000000001</v>
       </c>
       <c r="F81">
-        <v>46.373</v>
+        <v>46.96000000000001</v>
       </c>
       <c r="G81">
         <v>5.97</v>
@@ -7923,28 +7923,28 @@
         <v>6.935</v>
       </c>
       <c r="M81">
-        <v>4.173570000000001</v>
+        <v>4.226400000000001</v>
       </c>
       <c r="N81">
-        <v>2.761429999999999</v>
+        <v>2.708599999999999</v>
       </c>
       <c r="O81">
-        <v>0.5522859999999998</v>
+        <v>0.5417199999999998</v>
       </c>
       <c r="P81">
-        <v>2.209143999999999</v>
+        <v>2.166879999999999</v>
       </c>
       <c r="Q81">
-        <v>4.599143999999999</v>
+        <v>4.556879999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2528936389049007</v>
+        <v>0.262731816525086</v>
       </c>
       <c r="T81">
-        <v>3.928489804191967</v>
+        <v>4.115116398215338</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.661646983278104</v>
+        <v>1.640876395987128</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1101463633050172</v>
+        <v>0.1103050624400052</v>
       </c>
       <c r="C82">
-        <v>-0.4479372290336983</v>
+        <v>-1.134681187864324</v>
       </c>
       <c r="D82">
-        <v>40.54206277096631</v>
+        <v>40.44231881213568</v>
       </c>
       <c r="E82">
-        <v>17.26000000000001</v>
+        <v>17.847</v>
       </c>
       <c r="F82">
-        <v>46.96000000000001</v>
+        <v>47.547</v>
       </c>
       <c r="G82">
         <v>5.97</v>
@@ -8005,28 +8005,28 @@
         <v>6.935</v>
       </c>
       <c r="M82">
-        <v>4.226400000000001</v>
+        <v>4.27923</v>
       </c>
       <c r="N82">
-        <v>2.708599999999999</v>
+        <v>2.65577</v>
       </c>
       <c r="O82">
-        <v>0.5417199999999998</v>
+        <v>0.5311539999999999</v>
       </c>
       <c r="P82">
-        <v>2.166879999999999</v>
+        <v>2.124616</v>
       </c>
       <c r="Q82">
-        <v>4.556879999999999</v>
+        <v>4.514615999999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.262731816525086</v>
+        <v>0.2736055917895013</v>
       </c>
       <c r="T82">
-        <v>4.115116398215338</v>
+        <v>4.321387896872749</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.640876395987128</v>
+        <v>1.620618662703337</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1103050624400052</v>
+        <v>0.1104637615749933</v>
       </c>
       <c r="C83">
-        <v>-1.134681187864324</v>
+        <v>-1.820935559340285</v>
       </c>
       <c r="D83">
-        <v>40.44231881213568</v>
+        <v>40.34306444065972</v>
       </c>
       <c r="E83">
-        <v>17.847</v>
+        <v>18.43400000000001</v>
       </c>
       <c r="F83">
-        <v>47.547</v>
+        <v>48.13400000000001</v>
       </c>
       <c r="G83">
         <v>5.97</v>
@@ -8087,28 +8087,28 @@
         <v>6.935</v>
       </c>
       <c r="M83">
-        <v>4.27923</v>
+        <v>4.33206</v>
       </c>
       <c r="N83">
-        <v>2.65577</v>
+        <v>2.602939999999999</v>
       </c>
       <c r="O83">
-        <v>0.5311539999999999</v>
+        <v>0.5205879999999999</v>
       </c>
       <c r="P83">
-        <v>2.124616</v>
+        <v>2.082351999999999</v>
       </c>
       <c r="Q83">
-        <v>4.514615999999999</v>
+        <v>4.472351999999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2736055917895013</v>
+        <v>0.2856875643055184</v>
       </c>
       <c r="T83">
-        <v>4.321387896872749</v>
+        <v>4.550578450936538</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.620618662703337</v>
+        <v>1.600855020475247</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1104637615749933</v>
+        <v>0.1106224607099814</v>
       </c>
       <c r="C84">
-        <v>-1.820935559340285</v>
+        <v>-2.506703939302668</v>
       </c>
       <c r="D84">
-        <v>40.34306444065972</v>
+        <v>40.24429606069734</v>
       </c>
       <c r="E84">
-        <v>18.43400000000001</v>
+        <v>19.021</v>
       </c>
       <c r="F84">
-        <v>48.13400000000001</v>
+        <v>48.721</v>
       </c>
       <c r="G84">
         <v>5.97</v>
@@ -8169,28 +8169,28 @@
         <v>6.935</v>
       </c>
       <c r="M84">
-        <v>4.33206</v>
+        <v>4.38489</v>
       </c>
       <c r="N84">
-        <v>2.602939999999999</v>
+        <v>2.550109999999999</v>
       </c>
       <c r="O84">
-        <v>0.5205879999999999</v>
+        <v>0.5100219999999999</v>
       </c>
       <c r="P84">
-        <v>2.082351999999999</v>
+        <v>2.040087999999999</v>
       </c>
       <c r="Q84">
-        <v>4.472351999999999</v>
+        <v>4.430088</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2856875643055184</v>
+        <v>0.2991909453528316</v>
       </c>
       <c r="T84">
-        <v>4.550578450936538</v>
+        <v>4.806732599596068</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.600855020475247</v>
+        <v>1.581567610590003</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1106224607099814</v>
+        <v>0.1107811598449694</v>
       </c>
       <c r="C85">
-        <v>-2.506703939302668</v>
+        <v>-3.191989888465059</v>
       </c>
       <c r="D85">
-        <v>40.24429606069734</v>
+        <v>40.14601011153495</v>
       </c>
       <c r="E85">
-        <v>19.021</v>
+        <v>19.60800000000001</v>
       </c>
       <c r="F85">
-        <v>48.721</v>
+        <v>49.30800000000001</v>
       </c>
       <c r="G85">
         <v>5.97</v>
@@ -8251,28 +8251,28 @@
         <v>6.935</v>
       </c>
       <c r="M85">
-        <v>4.38489</v>
+        <v>4.437720000000001</v>
       </c>
       <c r="N85">
-        <v>2.550109999999999</v>
+        <v>2.497279999999999</v>
       </c>
       <c r="O85">
-        <v>0.5100219999999999</v>
+        <v>0.4994559999999998</v>
       </c>
       <c r="P85">
-        <v>2.040087999999999</v>
+        <v>1.997823999999999</v>
       </c>
       <c r="Q85">
-        <v>4.430088</v>
+        <v>4.387823999999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2991909453528316</v>
+        <v>0.3143822490310589</v>
       </c>
       <c r="T85">
-        <v>4.806732599596068</v>
+        <v>5.094906016838039</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.581567610590003</v>
+        <v>1.562739424749646</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1107811598449694</v>
+        <v>0.1109398589799575</v>
       </c>
       <c r="C86">
-        <v>-3.191989888465052</v>
+        <v>-3.876796932841408</v>
       </c>
       <c r="D86">
-        <v>40.14601011153495</v>
+        <v>40.0482030671586</v>
       </c>
       <c r="E86">
-        <v>19.608</v>
+        <v>20.195</v>
       </c>
       <c r="F86">
-        <v>49.308</v>
+        <v>49.895</v>
       </c>
       <c r="G86">
         <v>5.97</v>
@@ -8333,28 +8333,28 @@
         <v>6.935</v>
       </c>
       <c r="M86">
-        <v>4.43772</v>
+        <v>4.49055</v>
       </c>
       <c r="N86">
-        <v>2.49728</v>
+        <v>2.44445</v>
       </c>
       <c r="O86">
-        <v>0.499456</v>
+        <v>0.48889</v>
       </c>
       <c r="P86">
-        <v>1.997824</v>
+        <v>1.95556</v>
       </c>
       <c r="Q86">
-        <v>4.387824</v>
+        <v>4.345559999999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3143822490310588</v>
+        <v>0.3315990598663831</v>
       </c>
       <c r="T86">
-        <v>5.094906016838036</v>
+        <v>5.421502556378936</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.562739424749646</v>
+        <v>1.544354255046709</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1109398589799575</v>
+        <v>0.1110985581149455</v>
       </c>
       <c r="C87">
-        <v>-3.876796932841408</v>
+        <v>-4.561128564167724</v>
       </c>
       <c r="D87">
-        <v>40.0482030671586</v>
+        <v>39.95087143583228</v>
       </c>
       <c r="E87">
-        <v>20.195</v>
+        <v>20.782</v>
       </c>
       <c r="F87">
-        <v>49.895</v>
+        <v>50.482</v>
       </c>
       <c r="G87">
         <v>5.97</v>
@@ -8415,28 +8415,28 @@
         <v>6.935</v>
       </c>
       <c r="M87">
-        <v>4.49055</v>
+        <v>4.54338</v>
       </c>
       <c r="N87">
-        <v>2.44445</v>
+        <v>2.39162</v>
       </c>
       <c r="O87">
-        <v>0.48889</v>
+        <v>0.478324</v>
       </c>
       <c r="P87">
-        <v>1.95556</v>
+        <v>1.913296</v>
       </c>
       <c r="Q87">
-        <v>4.345559999999999</v>
+        <v>4.303296</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3315990598663831</v>
+        <v>0.3512754151067537</v>
       </c>
       <c r="T87">
-        <v>5.421502556378936</v>
+        <v>5.794755744425679</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.544354255046709</v>
+        <v>1.526396647429887</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1110985581149455</v>
+        <v>0.1112572572499336</v>
       </c>
       <c r="C88">
-        <v>-4.561128564167724</v>
+        <v>-5.244988240317575</v>
       </c>
       <c r="D88">
-        <v>39.95087143583228</v>
+        <v>39.85401175968243</v>
       </c>
       <c r="E88">
-        <v>20.782</v>
+        <v>21.369</v>
       </c>
       <c r="F88">
-        <v>50.482</v>
+        <v>51.069</v>
       </c>
       <c r="G88">
         <v>5.97</v>
@@ -8497,28 +8497,28 @@
         <v>6.935</v>
       </c>
       <c r="M88">
-        <v>4.54338</v>
+        <v>4.59621</v>
       </c>
       <c r="N88">
-        <v>2.39162</v>
+        <v>2.338789999999999</v>
       </c>
       <c r="O88">
-        <v>0.478324</v>
+        <v>0.4677579999999999</v>
       </c>
       <c r="P88">
-        <v>1.913296</v>
+        <v>1.871032</v>
       </c>
       <c r="Q88">
-        <v>4.303296</v>
+        <v>4.261031999999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3512754151067537</v>
+        <v>0.3739789019225659</v>
       </c>
       <c r="T88">
-        <v>5.794755744425679</v>
+        <v>6.225432499864228</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.526396647429887</v>
+        <v>1.508851858378969</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1112572572499336</v>
+        <v>0.1543882671190258</v>
       </c>
       <c r="C89">
-        <v>-5.244988240317575</v>
+        <v>-21.66191001856653</v>
       </c>
       <c r="D89">
-        <v>39.85401175968243</v>
+        <v>24.02408998143347</v>
       </c>
       <c r="E89">
-        <v>21.369</v>
+        <v>21.95600000000001</v>
       </c>
       <c r="F89">
-        <v>51.069</v>
+        <v>51.65600000000001</v>
       </c>
       <c r="G89">
         <v>5.97</v>
@@ -8579,45 +8579,45 @@
         <v>6.935</v>
       </c>
       <c r="M89">
-        <v>4.59621</v>
+        <v>7.583100800000001</v>
       </c>
       <c r="N89">
-        <v>2.338789999999999</v>
+        <v>-0.6481008000000017</v>
       </c>
       <c r="O89">
-        <v>0.4677579999999999</v>
+        <v>-0.1296201600000003</v>
       </c>
       <c r="P89">
-        <v>1.871032</v>
+        <v>-0.5184806400000014</v>
       </c>
       <c r="Q89">
-        <v>4.261031999999999</v>
+        <v>1.871519359999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3739789019225659</v>
+        <v>0.4069407268436707</v>
       </c>
       <c r="T89">
-        <v>6.225432499864228</v>
+        <v>6.850706138469728</v>
       </c>
       <c r="U89">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2</v>
+        <v>0.1829067075041386</v>
       </c>
       <c r="W89">
-        <v>0.07199999999999999</v>
+        <v>0.1199492953383925</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.508851858378969</v>
+        <v>0.9145335375206932</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1543882671190258</v>
+        <v>0.1553982671190258</v>
       </c>
       <c r="C90">
-        <v>-21.66191001856653</v>
+        <v>-22.47030339931128</v>
       </c>
       <c r="D90">
-        <v>24.02408998143347</v>
+        <v>23.80269660068872</v>
       </c>
       <c r="E90">
-        <v>21.95600000000001</v>
+        <v>22.543</v>
       </c>
       <c r="F90">
-        <v>51.65600000000001</v>
+        <v>52.243</v>
       </c>
       <c r="G90">
         <v>5.97</v>
@@ -8661,37 +8661,37 @@
         <v>6.935</v>
       </c>
       <c r="M90">
-        <v>7.583100800000001</v>
+        <v>7.669272400000001</v>
       </c>
       <c r="N90">
-        <v>-0.6481008000000017</v>
+        <v>-0.7342724000000018</v>
       </c>
       <c r="O90">
-        <v>-0.1296201600000003</v>
+        <v>-0.1468544800000004</v>
       </c>
       <c r="P90">
-        <v>-0.5184806400000014</v>
+        <v>-0.5874179200000015</v>
       </c>
       <c r="Q90">
-        <v>1.871519359999998</v>
+        <v>1.802582079999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4069407268436707</v>
+        <v>0.4397717020112771</v>
       </c>
       <c r="T90">
-        <v>6.850706138469728</v>
+        <v>7.473497605603339</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1829067075041386</v>
+        <v>0.1808515759591483</v>
       </c>
       <c r="W90">
-        <v>0.1199492953383925</v>
+        <v>0.120250988649197</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9145335375206932</v>
+        <v>0.9042578797957416</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1553982671190258</v>
+        <v>0.1564082671190258</v>
       </c>
       <c r="C91">
-        <v>-22.47030339931128</v>
+        <v>-23.2746535503703</v>
       </c>
       <c r="D91">
-        <v>23.80269660068872</v>
+        <v>23.58534644962971</v>
       </c>
       <c r="E91">
-        <v>22.543</v>
+        <v>23.13000000000001</v>
       </c>
       <c r="F91">
-        <v>52.243</v>
+        <v>52.83000000000001</v>
       </c>
       <c r="G91">
         <v>5.97</v>
@@ -8743,37 +8743,37 @@
         <v>6.935</v>
       </c>
       <c r="M91">
-        <v>7.669272400000001</v>
+        <v>7.755444000000002</v>
       </c>
       <c r="N91">
-        <v>-0.7342724000000018</v>
+        <v>-0.8204440000000019</v>
       </c>
       <c r="O91">
-        <v>-0.1468544800000004</v>
+        <v>-0.1640888000000004</v>
       </c>
       <c r="P91">
-        <v>-0.5874179200000015</v>
+        <v>-0.6563552000000016</v>
       </c>
       <c r="Q91">
-        <v>1.802582079999998</v>
+        <v>1.733644799999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4397717020112771</v>
+        <v>0.479168872212405</v>
       </c>
       <c r="T91">
-        <v>7.473497605603339</v>
+        <v>8.220847366163676</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1808515759591483</v>
+        <v>0.1788421140040467</v>
       </c>
       <c r="W91">
-        <v>0.120250988649197</v>
+        <v>0.120545977664206</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9042578797957416</v>
+        <v>0.8942105700202333</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1564082671190258</v>
+        <v>0.1574182671190258</v>
       </c>
       <c r="C92">
-        <v>-23.2746535503703</v>
+        <v>-24.07507022963771</v>
       </c>
       <c r="D92">
-        <v>23.58534644962971</v>
+        <v>23.37192977036229</v>
       </c>
       <c r="E92">
-        <v>23.13000000000001</v>
+        <v>23.717</v>
       </c>
       <c r="F92">
-        <v>52.83000000000001</v>
+        <v>53.417</v>
       </c>
       <c r="G92">
         <v>5.97</v>
@@ -8825,37 +8825,37 @@
         <v>6.935</v>
       </c>
       <c r="M92">
-        <v>7.755444000000002</v>
+        <v>7.841615600000001</v>
       </c>
       <c r="N92">
-        <v>-0.8204440000000019</v>
+        <v>-0.9066156000000012</v>
       </c>
       <c r="O92">
-        <v>-0.1640888000000004</v>
+        <v>-0.1813231200000003</v>
       </c>
       <c r="P92">
-        <v>-0.6563552000000016</v>
+        <v>-0.7252924800000009</v>
       </c>
       <c r="Q92">
-        <v>1.733644799999998</v>
+        <v>1.664707519999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.479168872212405</v>
+        <v>0.5273209691248943</v>
       </c>
       <c r="T92">
-        <v>8.220847366163676</v>
+        <v>9.134274851292972</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1788421140040467</v>
+        <v>0.1768768160479583</v>
       </c>
       <c r="W92">
-        <v>0.120545977664206</v>
+        <v>0.1208344834041597</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8942105700202333</v>
+        <v>0.8843840802397913</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1574182671190258</v>
+        <v>0.1584282671190259</v>
       </c>
       <c r="C93">
-        <v>-24.07507022963771</v>
+        <v>-24.87165925796858</v>
       </c>
       <c r="D93">
-        <v>23.37192977036229</v>
+        <v>23.16234074203142</v>
       </c>
       <c r="E93">
-        <v>23.717</v>
+        <v>24.30400000000001</v>
       </c>
       <c r="F93">
-        <v>53.417</v>
+        <v>54.004</v>
       </c>
       <c r="G93">
         <v>5.97</v>
@@ -8907,37 +8907,37 @@
         <v>6.935</v>
       </c>
       <c r="M93">
-        <v>7.841615600000001</v>
+        <v>7.927787200000002</v>
       </c>
       <c r="N93">
-        <v>-0.9066156000000012</v>
+        <v>-0.9927872000000022</v>
       </c>
       <c r="O93">
-        <v>-0.1813231200000003</v>
+        <v>-0.1985574400000004</v>
       </c>
       <c r="P93">
-        <v>-0.7252924800000009</v>
+        <v>-0.7942297600000018</v>
       </c>
       <c r="Q93">
-        <v>1.664707519999999</v>
+        <v>1.595770239999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5273209691248943</v>
+        <v>0.5875110902655063</v>
       </c>
       <c r="T93">
-        <v>9.134274851292972</v>
+        <v>10.2760592077046</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1768768160479583</v>
+        <v>0.1749542419604804</v>
       </c>
       <c r="W93">
-        <v>0.1208344834041597</v>
+        <v>0.1211167172802015</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8843840802397913</v>
+        <v>0.8747712098024021</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1584282671190259</v>
+        <v>0.1594382671190259</v>
       </c>
       <c r="C94">
-        <v>-24.87165925796858</v>
+        <v>-25.66452269413793</v>
       </c>
       <c r="D94">
-        <v>23.16234074203142</v>
+        <v>22.95647730586208</v>
       </c>
       <c r="E94">
-        <v>24.30400000000001</v>
+        <v>24.89100000000001</v>
       </c>
       <c r="F94">
-        <v>54.004</v>
+        <v>54.59100000000001</v>
       </c>
       <c r="G94">
         <v>5.97</v>
@@ -8989,37 +8989,37 @@
         <v>6.935</v>
       </c>
       <c r="M94">
-        <v>7.927787200000002</v>
+        <v>8.013958800000003</v>
       </c>
       <c r="N94">
-        <v>-0.9927872000000022</v>
+        <v>-1.078958800000003</v>
       </c>
       <c r="O94">
-        <v>-0.1985574400000004</v>
+        <v>-0.2157917600000007</v>
       </c>
       <c r="P94">
-        <v>-0.7942297600000018</v>
+        <v>-0.8631670400000026</v>
       </c>
       <c r="Q94">
-        <v>1.595770239999998</v>
+        <v>1.526832959999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5875110902655063</v>
+        <v>0.6648983888748644</v>
       </c>
       <c r="T94">
-        <v>10.2760592077046</v>
+        <v>11.74406766594811</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1749542419604804</v>
+        <v>0.1730730135523032</v>
       </c>
       <c r="W94">
-        <v>0.1211167172802015</v>
+        <v>0.1213928816105219</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8747712098024021</v>
+        <v>0.865365067761516</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1594382671190259</v>
+        <v>0.1604482671190259</v>
       </c>
       <c r="C95">
-        <v>-25.66452269413793</v>
+        <v>-26.45375900055195</v>
       </c>
       <c r="D95">
-        <v>22.95647730586208</v>
+        <v>22.75424099944806</v>
       </c>
       <c r="E95">
-        <v>24.89100000000001</v>
+        <v>25.47800000000001</v>
       </c>
       <c r="F95">
-        <v>54.59100000000001</v>
+        <v>55.178</v>
       </c>
       <c r="G95">
         <v>5.97</v>
@@ -9071,37 +9071,37 @@
         <v>6.935</v>
       </c>
       <c r="M95">
-        <v>8.013958800000003</v>
+        <v>8.100130400000001</v>
       </c>
       <c r="N95">
-        <v>-1.078958800000003</v>
+        <v>-1.165130400000002</v>
       </c>
       <c r="O95">
-        <v>-0.2157917600000007</v>
+        <v>-0.2330260800000003</v>
       </c>
       <c r="P95">
-        <v>-0.8631670400000026</v>
+        <v>-0.9321043200000012</v>
       </c>
       <c r="Q95">
-        <v>1.526832959999997</v>
+        <v>1.457895679999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6648983888748644</v>
+        <v>0.7680814536873419</v>
       </c>
       <c r="T95">
-        <v>11.74406766594811</v>
+        <v>13.70141227693947</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1730730135523032</v>
+        <v>0.1712318112804702</v>
       </c>
       <c r="W95">
-        <v>0.1213928816105219</v>
+        <v>0.121663170104027</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.865365067761516</v>
+        <v>0.8561590564023511</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1604482671190259</v>
+        <v>0.1614582671190259</v>
       </c>
       <c r="C96">
-        <v>-26.45375900055195</v>
+        <v>-27.23946320027675</v>
       </c>
       <c r="D96">
-        <v>22.75424099944806</v>
+        <v>22.55553679972326</v>
       </c>
       <c r="E96">
-        <v>25.47800000000001</v>
+        <v>26.06500000000001</v>
       </c>
       <c r="F96">
-        <v>55.178</v>
+        <v>55.76500000000001</v>
       </c>
       <c r="G96">
         <v>5.97</v>
@@ -9153,37 +9153,37 @@
         <v>6.935</v>
       </c>
       <c r="M96">
-        <v>8.100130400000001</v>
+        <v>8.186302000000001</v>
       </c>
       <c r="N96">
-        <v>-1.165130400000002</v>
+        <v>-1.251302000000002</v>
       </c>
       <c r="O96">
-        <v>-0.2330260800000003</v>
+        <v>-0.2502604000000003</v>
       </c>
       <c r="P96">
-        <v>-0.9321043200000012</v>
+        <v>-1.001041600000001</v>
       </c>
       <c r="Q96">
-        <v>1.457895679999998</v>
+        <v>1.388958399999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7680814536873419</v>
+        <v>0.9125377444248111</v>
       </c>
       <c r="T96">
-        <v>13.70141227693947</v>
+        <v>16.44169473232737</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1712318112804702</v>
+        <v>0.1694293711617284</v>
       </c>
       <c r="W96">
-        <v>0.121663170104027</v>
+        <v>0.1219277683134583</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8561590564023511</v>
+        <v>0.8471468558086421</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1614582671190259</v>
+        <v>0.1624682671190258</v>
       </c>
       <c r="C97">
-        <v>-27.23946320027675</v>
+        <v>-28.02172702591049</v>
       </c>
       <c r="D97">
-        <v>22.55553679972326</v>
+        <v>22.36027297408951</v>
       </c>
       <c r="E97">
-        <v>26.06500000000001</v>
+        <v>26.652</v>
       </c>
       <c r="F97">
-        <v>55.76500000000001</v>
+        <v>56.352</v>
       </c>
       <c r="G97">
         <v>5.97</v>
@@ -9235,37 +9235,37 @@
         <v>6.935</v>
       </c>
       <c r="M97">
-        <v>8.186302000000001</v>
+        <v>8.272473600000001</v>
       </c>
       <c r="N97">
-        <v>-1.251302000000002</v>
+        <v>-1.337473600000002</v>
       </c>
       <c r="O97">
-        <v>-0.2502604000000003</v>
+        <v>-0.2674947200000004</v>
       </c>
       <c r="P97">
-        <v>-1.001041600000001</v>
+        <v>-1.069978880000001</v>
       </c>
       <c r="Q97">
-        <v>1.388958399999998</v>
+        <v>1.320021119999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9125377444248111</v>
+        <v>1.129222180531014</v>
       </c>
       <c r="T97">
-        <v>16.44169473232737</v>
+        <v>20.55211841540922</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1694293711617284</v>
+        <v>0.1676644818787938</v>
       </c>
       <c r="W97">
-        <v>0.1219277683134583</v>
+        <v>0.1221868540601931</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8471468558086421</v>
+        <v>0.8383224093939687</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1624682671190258</v>
+        <v>0.1634782671190259</v>
       </c>
       <c r="C98">
-        <v>-28.02172702591049</v>
+        <v>-28.80063906078935</v>
       </c>
       <c r="D98">
-        <v>22.36027297408951</v>
+        <v>22.16836093921065</v>
       </c>
       <c r="E98">
-        <v>26.652</v>
+        <v>27.239</v>
       </c>
       <c r="F98">
-        <v>56.352</v>
+        <v>56.939</v>
       </c>
       <c r="G98">
         <v>5.97</v>
@@ -9317,37 +9317,37 @@
         <v>6.935</v>
       </c>
       <c r="M98">
-        <v>8.272473600000001</v>
+        <v>8.358645200000002</v>
       </c>
       <c r="N98">
-        <v>-1.337473600000002</v>
+        <v>-1.423645200000002</v>
       </c>
       <c r="O98">
-        <v>-0.2674947200000004</v>
+        <v>-0.2847290400000004</v>
       </c>
       <c r="P98">
-        <v>-1.069978880000001</v>
+        <v>-1.138916160000002</v>
       </c>
       <c r="Q98">
-        <v>1.320021119999998</v>
+        <v>1.251083839999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.129222180531011</v>
+        <v>1.490362907374682</v>
       </c>
       <c r="T98">
-        <v>20.55211841540916</v>
+        <v>27.40282455387889</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1676644818787938</v>
+        <v>0.1659359820656103</v>
       </c>
       <c r="W98">
-        <v>0.1221868540601931</v>
+        <v>0.1224405978327684</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8383224093939687</v>
+        <v>0.8296799103280516</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1634782671190259</v>
+        <v>0.1644882671190258</v>
       </c>
       <c r="C99">
-        <v>-28.80063906078935</v>
+        <v>-29.57628487298365</v>
       </c>
       <c r="D99">
-        <v>22.16836093921065</v>
+        <v>21.97971512701636</v>
       </c>
       <c r="E99">
-        <v>27.239</v>
+        <v>27.826</v>
       </c>
       <c r="F99">
-        <v>56.939</v>
+        <v>57.526</v>
       </c>
       <c r="G99">
         <v>5.97</v>
@@ -9399,37 +9399,37 @@
         <v>6.935</v>
       </c>
       <c r="M99">
-        <v>8.358645200000002</v>
+        <v>8.444816800000002</v>
       </c>
       <c r="N99">
-        <v>-1.423645200000002</v>
+        <v>-1.509816800000002</v>
       </c>
       <c r="O99">
-        <v>-0.2847290400000004</v>
+        <v>-0.3019633600000005</v>
       </c>
       <c r="P99">
-        <v>-1.138916160000002</v>
+        <v>-1.207853440000002</v>
       </c>
       <c r="Q99">
-        <v>1.251083839999998</v>
+        <v>1.182146559999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.490362907374682</v>
+        <v>2.212644361062022</v>
       </c>
       <c r="T99">
-        <v>27.40282455387889</v>
+        <v>41.10423683081833</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1659359820656103</v>
+        <v>0.1642427577588184</v>
       </c>
       <c r="W99">
-        <v>0.1224405978327684</v>
+        <v>0.1226891631610055</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8296799103280516</v>
+        <v>0.8212137887940918</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1644882671190258</v>
+        <v>0.1654982671190258</v>
       </c>
       <c r="C100">
-        <v>-29.57628487298365</v>
+        <v>-30.34874714251017</v>
       </c>
       <c r="D100">
-        <v>21.97971512701636</v>
+        <v>21.79425285748983</v>
       </c>
       <c r="E100">
-        <v>27.826</v>
+        <v>28.413</v>
       </c>
       <c r="F100">
-        <v>57.526</v>
+        <v>58.113</v>
       </c>
       <c r="G100">
         <v>5.97</v>
@@ -9481,37 +9481,37 @@
         <v>6.935</v>
       </c>
       <c r="M100">
-        <v>8.444816800000002</v>
+        <v>8.5309884</v>
       </c>
       <c r="N100">
-        <v>-1.509816800000002</v>
+        <v>-1.5959884</v>
       </c>
       <c r="O100">
-        <v>-0.3019633600000005</v>
+        <v>-0.3191976800000001</v>
       </c>
       <c r="P100">
-        <v>-1.207853440000002</v>
+        <v>-1.27679072</v>
       </c>
       <c r="Q100">
-        <v>1.182146559999998</v>
+        <v>1.113209279999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.212644361062022</v>
+        <v>4.379488722124044</v>
       </c>
       <c r="T100">
-        <v>41.10423683081833</v>
+        <v>82.20847366163666</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1642427577588184</v>
+        <v>0.1625837400036788</v>
       </c>
       <c r="W100">
-        <v>0.1226891631610055</v>
+        <v>0.12293270696746</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8212137887940918</v>
+        <v>0.8129187000183941</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1654982671190258</v>
-      </c>
-      <c r="C101">
-        <v>-30.34874714251017</v>
-      </c>
-      <c r="D101">
-        <v>21.79425285748983</v>
-      </c>
-      <c r="E101">
-        <v>28.413</v>
-      </c>
-      <c r="F101">
-        <v>58.113</v>
-      </c>
-      <c r="G101">
-        <v>5.97</v>
-      </c>
-      <c r="H101">
-        <v>29</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.324999999999999</v>
-      </c>
-      <c r="K101">
-        <v>2.39</v>
-      </c>
-      <c r="L101">
-        <v>6.935</v>
-      </c>
-      <c r="M101">
-        <v>8.5309884</v>
-      </c>
-      <c r="N101">
-        <v>-1.5959884</v>
-      </c>
-      <c r="O101">
-        <v>-0.3191976800000001</v>
-      </c>
-      <c r="P101">
-        <v>-1.27679072</v>
-      </c>
-      <c r="Q101">
-        <v>1.113209279999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.379488722124044</v>
-      </c>
-      <c r="T101">
-        <v>82.20847366163666</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1625837400036788</v>
-      </c>
-      <c r="W101">
-        <v>0.12293270696746</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8129187000183941</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
